--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>AWB</t>
   </si>
@@ -34,172 +34,154 @@
     <t>Produto</t>
   </si>
   <si>
+    <t>3320095321733</t>
+  </si>
+  <si>
+    <t>3320028356609</t>
+  </si>
+  <si>
+    <t>3320042347162</t>
+  </si>
+  <si>
+    <t>3320074339155</t>
+  </si>
+  <si>
     <t>3320055330825</t>
   </si>
   <si>
-    <t>3320042347162</t>
+    <t>3320039311527</t>
+  </si>
+  <si>
+    <t>3320067343554</t>
   </si>
   <si>
     <t>3320069318689</t>
   </si>
   <si>
-    <t>3320095321733</t>
-  </si>
-  <si>
     <t>3320075338160</t>
   </si>
   <si>
-    <t>3320067343554</t>
-  </si>
-  <si>
-    <t>3320028356609</t>
-  </si>
-  <si>
-    <t>3320074339155</t>
-  </si>
-  <si>
-    <t>3320039311527</t>
-  </si>
-  <si>
-    <t>3320058340829</t>
+    <t>(JML INT) YURI ANTONIO - PRATA</t>
+  </si>
+  <si>
+    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
+  </si>
+  <si>
+    <t>(JML INT) RAFAEL MOREIRA - PRATA</t>
+  </si>
+  <si>
+    <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
   </si>
   <si>
     <t>(STB LOC) MYLENA SILVEIRA GONCALVES</t>
   </si>
   <si>
-    <t>(JML INT) RAFAEL MOREIRA - PRATA</t>
+    <t>(JML LOC) THALLES GOMES VIANA</t>
   </si>
   <si>
     <t>(JML INT)WHEMES LEMOS - SÃO GONÇALO</t>
   </si>
   <si>
-    <t>(JML INT) YURI ANTONIO - PRATA</t>
-  </si>
-  <si>
     <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
   </si>
   <si>
-    <t>(JML LOC) THALLES GOMES VIANA</t>
-  </si>
-  <si>
-    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
-  </si>
-  <si>
-    <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-  </si>
-  <si>
-    <t>(JML INT)WINDISON MAICON - ITABIRA</t>
+    <t>Sabrina Arthuso</t>
+  </si>
+  <si>
+    <t>Eduarda</t>
+  </si>
+  <si>
+    <t>nicca</t>
+  </si>
+  <si>
+    <t>laccia</t>
   </si>
   <si>
     <t>Vandreia Deia</t>
   </si>
   <si>
-    <t>nicca</t>
+    <t>joão guilherme</t>
   </si>
   <si>
     <t>Tereza Moreira da Silva Souza</t>
   </si>
   <si>
-    <t>Sabrina Arthuso</t>
-  </si>
-  <si>
     <t>Cristiane Ferreira Penna Carvalho</t>
   </si>
   <si>
-    <t>joão guilherme</t>
-  </si>
-  <si>
-    <t>Eduarda</t>
-  </si>
-  <si>
-    <t>laccia</t>
-  </si>
-  <si>
-    <t>Bernardo Trivelato</t>
+    <t>+5531996463846</t>
+  </si>
+  <si>
+    <t>+5531993769655</t>
+  </si>
+  <si>
+    <t>+5531971180166</t>
+  </si>
+  <si>
+    <t>+5531996366300</t>
   </si>
   <si>
     <t>+5531971220095</t>
   </si>
   <si>
-    <t>+5531971180166</t>
+    <t>+5531997320093</t>
   </si>
   <si>
     <t>+5531999507524</t>
   </si>
   <si>
-    <t>+5531996463846</t>
-  </si>
-  <si>
     <t>+5531971706341</t>
   </si>
   <si>
-    <t>+5531997320093</t>
-  </si>
-  <si>
-    <t>+5531993769655</t>
-  </si>
-  <si>
-    <t>+5531996366300</t>
-  </si>
-  <si>
-    <t>+5531995787387</t>
+    <t>Rua Egidio zanette 139 Casa, Dona julieta, São Domingos do Prata</t>
+  </si>
+  <si>
+    <t>Rua Caetés 133, Industrial, João Monlevade</t>
+  </si>
+  <si>
+    <t>Paulo rolla 58, ceramica, São Domingos do Prata</t>
+  </si>
+  <si>
+    <t>Rua prefeito Peraclito Americano 159 Casa, Baixa verde, Dionísio</t>
   </si>
   <si>
     <t>Rua Ermantino Correia 96 Casa, São Veríssimo, Santa Bárbara</t>
   </si>
   <si>
-    <t>Paulo rolla 58, ceramica, São Domingos do Prata</t>
+    <t>Rua Olga Krupp Silva 103 103, Vale da Serra, João Monlevade</t>
   </si>
   <si>
     <t>Rua Emílio Gomes 28 casa, Guanabara, São Gonçalo do Rio Abaixo</t>
   </si>
   <si>
-    <t>Rua Egidio zanette 139 Casa, Dona julieta, São Domingos do Prata</t>
-  </si>
-  <si>
     <t>José Antônio Nascimento 162 casa, Centro, Sem-Peixe</t>
   </si>
   <si>
-    <t>Rua Olga Krupp Silva 103 103, Vale da Serra, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Caetés 133, Industrial, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua prefeito Peraclito Americano 159 Casa, Baixa verde, Dionísio</t>
-  </si>
-  <si>
-    <t>Rua Afonso de Assis Freitas 361 Apt 301 bloco 5, Abóboras, Itabira</t>
+    <t>Blusa Premium Ideal para Academia em Vários Cores e Estilos Confortáveis*1</t>
+  </si>
+  <si>
+    <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
+  </si>
+  <si>
+    <t>Calcinha de Emagrecimento / Cinta Modeladora / Roupa Íntima / Afina a Barriga Leggings Calça*1</t>
+  </si>
+  <si>
+    <t>Conjunto de Trem de Madeira com Números, Inclui Locomotiva e Vagões para Meninos e Meninas*1</t>
   </si>
   <si>
     <t>Kit 3 Calcinhas Borboleta VERMELHA PRETA BRANCA Fio Dental Sexy Regulagem Sensual Lingerie Feminina Tanga*1</t>
   </si>
   <si>
-    <t>Calcinha de Emagrecimento / Cinta Modeladora / Roupa Íntima / Afina a Barriga Leggings Calça*1</t>
+    <t>Body Feminino Mula Manca com Gola Alta Moda Verão Praia*1</t>
+  </si>
+  <si>
+    <t>Placa Gua Sha Massagem Facial Pedra Anti Ruga Em Aço Inox - Skin Care*1</t>
   </si>
   <si>
     <t>5 Pcs Bracelete Confortável Incomparável Para Uso Diário Leveza Absoluta E Acabamento Impecável Acompanha Qualquer Ocasião*1</t>
   </si>
   <si>
-    <t>Blusa Premium Ideal para Academia em Vários Cores e Estilos Confortáveis*1</t>
-  </si>
-  <si>
     <t>Short Saia Plus Size Anarruga Feminino G1 ao G6 – Moda Conforto Estilo Casual*1+Short Saia Plus Size Anarruga Feminino G1 ao G6 – Moda Conforto Estilo Casual*1</t>
-  </si>
-  <si>
-    <t>Placa Gua Sha Massagem Facial Pedra Anti Ruga Em Aço Inox - Skin Care*1</t>
-  </si>
-  <si>
-    <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
-  </si>
-  <si>
-    <t>Conjunto de Trem de Madeira com Números, Inclui Locomotiva e Vagões para Meninos e Meninas*1</t>
-  </si>
-  <si>
-    <t>Body Feminino Mula Manca com Gola Alta Moda Verão Praia*1</t>
-  </si>
-  <si>
-    <t>Kit 3 ou 6 Pares Meias Futebol Antiderrapantes meia canela futsal*1</t>
   </si>
 </sst>
 </file>
@@ -531,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -559,19 +541,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -579,19 +561,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -599,19 +581,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -619,19 +601,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -639,19 +621,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -659,19 +641,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>48</v>
-      </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -679,19 +661,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -699,19 +681,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -719,39 +701,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
         <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>AWB</t>
   </si>
@@ -37,151 +37,259 @@
     <t>3320095321733</t>
   </si>
   <si>
+    <t>3320072358688</t>
+  </si>
+  <si>
+    <t>3320085334706</t>
+  </si>
+  <si>
+    <t>3320055330825</t>
+  </si>
+  <si>
+    <t>3320033358219</t>
+  </si>
+  <si>
+    <t>3320022360871</t>
+  </si>
+  <si>
+    <t>3320022349122</t>
+  </si>
+  <si>
+    <t>3320067343554</t>
+  </si>
+  <si>
+    <t>3320077355443</t>
+  </si>
+  <si>
+    <t>3320096343566</t>
+  </si>
+  <si>
+    <t>3320091356100</t>
+  </si>
+  <si>
+    <t>3320097353925</t>
+  </si>
+  <si>
+    <t>3320039311527</t>
+  </si>
+  <si>
+    <t>3320042347162</t>
+  </si>
+  <si>
+    <t>3320019348079</t>
+  </si>
+  <si>
     <t>3320028356609</t>
   </si>
   <si>
-    <t>3320042347162</t>
-  </si>
-  <si>
-    <t>3320074339155</t>
-  </si>
-  <si>
-    <t>3320055330825</t>
-  </si>
-  <si>
-    <t>3320039311527</t>
-  </si>
-  <si>
-    <t>3320067343554</t>
-  </si>
-  <si>
-    <t>3320069318689</t>
-  </si>
-  <si>
-    <t>3320075338160</t>
-  </si>
-  <si>
     <t>(JML INT) YURI ANTONIO - PRATA</t>
   </si>
   <si>
+    <t>(JML LOC)TIAGO SALES MENDES</t>
+  </si>
+  <si>
+    <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
+  </si>
+  <si>
+    <t>(STB LOC) MYLENA SILVEIRA GONCALVES</t>
+  </si>
+  <si>
     <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
   </si>
   <si>
+    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+  </si>
+  <si>
+    <t>(JML LOC) THALLES GOMES VIANA</t>
+  </si>
+  <si>
+    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
+  </si>
+  <si>
+    <t>(JML LOC) DANIEL SANTOS MOURA</t>
+  </si>
+  <si>
     <t>(JML INT) RAFAEL MOREIRA - PRATA</t>
   </si>
   <si>
-    <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-  </si>
-  <si>
-    <t>(STB LOC) MYLENA SILVEIRA GONCALVES</t>
-  </si>
-  <si>
-    <t>(JML LOC) THALLES GOMES VIANA</t>
-  </si>
-  <si>
-    <t>(JML INT)WHEMES LEMOS - SÃO GONÇALO</t>
-  </si>
-  <si>
-    <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
-  </si>
-  <si>
     <t>Sabrina Arthuso</t>
   </si>
   <si>
+    <t>Carolina Carvalho</t>
+  </si>
+  <si>
+    <t>Luciano Almeida Gonçalves</t>
+  </si>
+  <si>
+    <t>Vandreia Deia</t>
+  </si>
+  <si>
+    <t>jc.yxr7</t>
+  </si>
+  <si>
+    <t>diogo</t>
+  </si>
+  <si>
+    <t>Lari Lari</t>
+  </si>
+  <si>
+    <t>joão guilherme</t>
+  </si>
+  <si>
+    <t>Luiz Otavio Bastos</t>
+  </si>
+  <si>
+    <t>Kennedy Wander</t>
+  </si>
+  <si>
+    <t>Psi liberato</t>
+  </si>
+  <si>
+    <t>Edesio</t>
+  </si>
+  <si>
+    <t>nicca</t>
+  </si>
+  <si>
+    <t>milinha Vasconcellos</t>
+  </si>
+  <si>
     <t>Eduarda</t>
   </si>
   <si>
-    <t>nicca</t>
-  </si>
-  <si>
-    <t>laccia</t>
-  </si>
-  <si>
-    <t>Vandreia Deia</t>
-  </si>
-  <si>
-    <t>joão guilherme</t>
-  </si>
-  <si>
-    <t>Tereza Moreira da Silva Souza</t>
-  </si>
-  <si>
-    <t>Cristiane Ferreira Penna Carvalho</t>
-  </si>
-  <si>
     <t>+5531996463846</t>
   </si>
   <si>
+    <t>+5531992722136</t>
+  </si>
+  <si>
+    <t>+5531999789232</t>
+  </si>
+  <si>
+    <t>+5531971220095</t>
+  </si>
+  <si>
+    <t>+5531971962410</t>
+  </si>
+  <si>
+    <t>+5527981191289</t>
+  </si>
+  <si>
+    <t>+5531994361780</t>
+  </si>
+  <si>
+    <t>+5531997320093</t>
+  </si>
+  <si>
+    <t>+5531999473398</t>
+  </si>
+  <si>
+    <t>+5553191738884</t>
+  </si>
+  <si>
+    <t>+5531973103445</t>
+  </si>
+  <si>
+    <t>+5531989418896</t>
+  </si>
+  <si>
+    <t>+5531971180166</t>
+  </si>
+  <si>
+    <t>+5531982151895</t>
+  </si>
+  <si>
     <t>+5531993769655</t>
   </si>
   <si>
-    <t>+5531971180166</t>
-  </si>
-  <si>
-    <t>+5531996366300</t>
-  </si>
-  <si>
-    <t>+5531971220095</t>
-  </si>
-  <si>
-    <t>+5531997320093</t>
-  </si>
-  <si>
-    <t>+5531999507524</t>
-  </si>
-  <si>
-    <t>+5531971706341</t>
-  </si>
-  <si>
     <t>Rua Egidio zanette 139 Casa, Dona julieta, São Domingos do Prata</t>
   </si>
   <si>
+    <t>Rua Santa Mônica 64, José Elói, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Acre 357 casa, Barro Branco, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Ermantino Correia 96 Casa, São Veríssimo, Santa Bárbara</t>
+  </si>
+  <si>
+    <t>Monsenhor lelis 00 Casa, Santana do alfie, São Domingos do Prata</t>
+  </si>
+  <si>
+    <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
+  </si>
+  <si>
+    <t>Rua Olga Krupp Silva 103 103, Vale da Serra, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Padre Pedro Domingues 266 loja, Centro, São Domingos do Prata</t>
+  </si>
+  <si>
+    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Platina 19 101, Santa Bárbara, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Barão de Cocais 1100 1100 Apartamento 402 bloco 04, Nova Esperança, João Monlevade</t>
+  </si>
+  <si>
+    <t>Paulo rolla 58, ceramica, São Domingos do Prata</t>
+  </si>
+  <si>
+    <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
+  </si>
+  <si>
     <t>Rua Caetés 133, Industrial, João Monlevade</t>
   </si>
   <si>
-    <t>Paulo rolla 58, ceramica, São Domingos do Prata</t>
-  </si>
-  <si>
-    <t>Rua prefeito Peraclito Americano 159 Casa, Baixa verde, Dionísio</t>
-  </si>
-  <si>
-    <t>Rua Ermantino Correia 96 Casa, São Veríssimo, Santa Bárbara</t>
-  </si>
-  <si>
-    <t>Rua Olga Krupp Silva 103 103, Vale da Serra, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Emílio Gomes 28 casa, Guanabara, São Gonçalo do Rio Abaixo</t>
-  </si>
-  <si>
-    <t>José Antônio Nascimento 162 casa, Centro, Sem-Peixe</t>
-  </si>
-  <si>
     <t>Blusa Premium Ideal para Academia em Vários Cores e Estilos Confortáveis*1</t>
   </si>
   <si>
+    <t>Jogo De Lençol 2 e 3 Peças premium 400 fios Solteiro Casal Queen King*1+Jogo De Lençol 2 e 3 Peças premium 400 fios Solteiro Casal Queen King*1</t>
+  </si>
+  <si>
+    <t>Rastreador Chaveiro de Bagagem Mala PetAnti-Perda Mini Localizador Chaveiro GPS(Compatível com Android e iOS)*1</t>
+  </si>
+  <si>
+    <t>Kit 3 Calcinhas Borboleta VERMELHA PRETA BRANCA Fio Dental Sexy Regulagem Sensual Lingerie Feminina Tanga*1</t>
+  </si>
+  <si>
     <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
   </si>
   <si>
+    <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
+  </si>
+  <si>
+    <t>Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1</t>
+  </si>
+  <si>
+    <t>Placa Gua Sha Massagem Facial Pedra Anti Ruga Em Aço Inox - Skin Care*1</t>
+  </si>
+  <si>
+    <t>Carteira Masculina Couro Legitimo Slim Pequena Executiva de Bolso*1</t>
+  </si>
+  <si>
+    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
+  </si>
+  <si>
+    <t>Colar de camada dupla apresenta as letra do nome e um pingente em forma de coração, e é banhado a*1</t>
+  </si>
+  <si>
+    <t>Cinto Masculino de Couro Sintético com Fivela de Catraca – Elegância e Praticidade*1</t>
+  </si>
+  <si>
+    <t>Body Feminino Mula Manca com Gola Alta Moda Verão Praia*1</t>
+  </si>
+  <si>
     <t>Calcinha de Emagrecimento / Cinta Modeladora / Roupa Íntima / Afina a Barriga Leggings Calça*1</t>
   </si>
   <si>
-    <t>Conjunto de Trem de Madeira com Números, Inclui Locomotiva e Vagões para Meninos e Meninas*1</t>
-  </si>
-  <si>
-    <t>Kit 3 Calcinhas Borboleta VERMELHA PRETA BRANCA Fio Dental Sexy Regulagem Sensual Lingerie Feminina Tanga*1</t>
-  </si>
-  <si>
-    <t>Body Feminino Mula Manca com Gola Alta Moda Verão Praia*1</t>
-  </si>
-  <si>
-    <t>Placa Gua Sha Massagem Facial Pedra Anti Ruga Em Aço Inox - Skin Care*1</t>
-  </si>
-  <si>
-    <t>5 Pcs Bracelete Confortável Incomparável Para Uso Diário Leveza Absoluta E Acabamento Impecável Acompanha Qualquer Ocasião*1</t>
-  </si>
-  <si>
-    <t>Short Saia Plus Size Anarruga Feminino G1 ao G6 – Moda Conforto Estilo Casual*1+Short Saia Plus Size Anarruga Feminino G1 ao G6 – Moda Conforto Estilo Casual*1</t>
+    <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
   </si>
 </sst>
 </file>
@@ -513,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -541,19 +649,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -561,19 +669,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -581,19 +689,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -601,19 +709,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -621,19 +729,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -641,19 +749,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -661,19 +769,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -681,19 +789,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -704,16 +812,156 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
         <v>46</v>
       </c>
-      <c r="F10" t="s">
-        <v>55</v>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_776161F9F613C836C26108D6AD0B636E49FA9099" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08AA4311-B6CE-4FD4-9241-1B3D3BADD104}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="90">
   <si>
     <t>AWB</t>
   </si>
@@ -34,52 +45,61 @@
     <t>Produto</t>
   </si>
   <si>
-    <t>3320095321733</t>
+    <t>3320090345591</t>
+  </si>
+  <si>
+    <t>3320019348079</t>
+  </si>
+  <si>
+    <t>3320028356609</t>
+  </si>
+  <si>
+    <t>3320065314168</t>
+  </si>
+  <si>
+    <t>3320033358219</t>
+  </si>
+  <si>
+    <t>3320090359776</t>
   </si>
   <si>
     <t>3320072358688</t>
   </si>
   <si>
+    <t>3320057350290</t>
+  </si>
+  <si>
     <t>3320085334706</t>
   </si>
   <si>
-    <t>3320055330825</t>
-  </si>
-  <si>
-    <t>3320033358219</t>
+    <t>3320054347575</t>
+  </si>
+  <si>
+    <t>3320096343566</t>
+  </si>
+  <si>
+    <t>3320022349122</t>
+  </si>
+  <si>
+    <t>3320038351075</t>
+  </si>
+  <si>
+    <t>3320009365112</t>
   </si>
   <si>
     <t>3320022360871</t>
   </si>
   <si>
-    <t>3320022349122</t>
-  </si>
-  <si>
-    <t>3320067343554</t>
-  </si>
-  <si>
-    <t>3320077355443</t>
-  </si>
-  <si>
-    <t>3320096343566</t>
-  </si>
-  <si>
-    <t>3320091356100</t>
-  </si>
-  <si>
-    <t>3320097353925</t>
-  </si>
-  <si>
-    <t>3320039311527</t>
-  </si>
-  <si>
-    <t>3320042347162</t>
-  </si>
-  <si>
-    <t>3320019348079</t>
-  </si>
-  <si>
-    <t>3320028356609</t>
+    <t>(STB LOC) CARLOS VINICIOS EFIRMIANDO</t>
+  </si>
+  <si>
+    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+  </si>
+  <si>
+    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
+  </si>
+  <si>
+    <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
   </si>
   <si>
     <t>(JML INT) YURI ANTONIO - PRATA</t>
@@ -88,215 +108,200 @@
     <t>(JML LOC)TIAGO SALES MENDES</t>
   </si>
   <si>
+    <t>(JML INT) LUCAS SANTOS - ITABIRA</t>
+  </si>
+  <si>
     <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
   </si>
   <si>
-    <t>(STB LOC) MYLENA SILVEIRA GONCALVES</t>
-  </si>
-  <si>
-    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
-  </si>
-  <si>
-    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
-  </si>
-  <si>
-    <t>(JML LOC) THALLES GOMES VIANA</t>
-  </si>
-  <si>
     <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
   </si>
   <si>
-    <t>(JML LOC) DANIEL SANTOS MOURA</t>
-  </si>
-  <si>
-    <t>(JML INT) RAFAEL MOREIRA - PRATA</t>
-  </si>
-  <si>
-    <t>Sabrina Arthuso</t>
+    <t>(JML LOC) ROGER CARLOS BRAGA</t>
+  </si>
+  <si>
+    <t>Rafaela Meireles Coutinho</t>
+  </si>
+  <si>
+    <t>milinha Vasconcellos</t>
+  </si>
+  <si>
+    <t>Eduarda</t>
+  </si>
+  <si>
+    <t>daniloluz20</t>
+  </si>
+  <si>
+    <t>jc.yxr7</t>
+  </si>
+  <si>
+    <t>eneluciafreitas</t>
   </si>
   <si>
     <t>Carolina Carvalho</t>
   </si>
   <si>
+    <t>Jane kelly</t>
+  </si>
+  <si>
     <t>Luciano Almeida Gonçalves</t>
   </si>
   <si>
-    <t>Vandreia Deia</t>
-  </si>
-  <si>
-    <t>jc.yxr7</t>
+    <t>Robson Gonçalves de Almeida</t>
+  </si>
+  <si>
+    <t>Kennedy Wander</t>
+  </si>
+  <si>
+    <t>Lari Lari</t>
+  </si>
+  <si>
+    <t>kaw carvalho</t>
+  </si>
+  <si>
+    <t>Alexandra Santos</t>
   </si>
   <si>
     <t>diogo</t>
   </si>
   <si>
-    <t>Lari Lari</t>
-  </si>
-  <si>
-    <t>joão guilherme</t>
-  </si>
-  <si>
-    <t>Luiz Otavio Bastos</t>
-  </si>
-  <si>
-    <t>Kennedy Wander</t>
-  </si>
-  <si>
-    <t>Psi liberato</t>
-  </si>
-  <si>
-    <t>Edesio</t>
-  </si>
-  <si>
-    <t>nicca</t>
-  </si>
-  <si>
-    <t>milinha Vasconcellos</t>
-  </si>
-  <si>
-    <t>Eduarda</t>
-  </si>
-  <si>
-    <t>+5531996463846</t>
+    <t>+5531994061028</t>
+  </si>
+  <si>
+    <t>+5531982151895</t>
+  </si>
+  <si>
+    <t>+5531993769655</t>
+  </si>
+  <si>
+    <t>+5592982080755</t>
+  </si>
+  <si>
+    <t>+5531971962410</t>
+  </si>
+  <si>
+    <t>+5531998675818</t>
   </si>
   <si>
     <t>+5531992722136</t>
   </si>
   <si>
+    <t>+5531990708633</t>
+  </si>
+  <si>
     <t>+5531999789232</t>
   </si>
   <si>
-    <t>+5531971220095</t>
-  </si>
-  <si>
-    <t>+5531971962410</t>
+    <t>+5531998320772</t>
+  </si>
+  <si>
+    <t>+5553191738884</t>
+  </si>
+  <si>
+    <t>+5531994361780</t>
+  </si>
+  <si>
+    <t>+5553399944958</t>
+  </si>
+  <si>
+    <t>+5535998721133</t>
   </si>
   <si>
     <t>+5527981191289</t>
   </si>
   <si>
-    <t>+5531994361780</t>
-  </si>
-  <si>
-    <t>+5531997320093</t>
-  </si>
-  <si>
-    <t>+5531999473398</t>
-  </si>
-  <si>
-    <t>+5553191738884</t>
-  </si>
-  <si>
-    <t>+5531973103445</t>
-  </si>
-  <si>
-    <t>+5531989418896</t>
-  </si>
-  <si>
-    <t>+5531971180166</t>
-  </si>
-  <si>
-    <t>+5531982151895</t>
-  </si>
-  <si>
-    <t>+5531993769655</t>
-  </si>
-  <si>
-    <t>Rua Egidio zanette 139 Casa, Dona julieta, São Domingos do Prata</t>
+    <t>Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara</t>
+  </si>
+  <si>
+    <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Caetés 133, Industrial, João Monlevade</t>
+  </si>
+  <si>
+    <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
+  </si>
+  <si>
+    <t>Monsenhor lelis 00 Casa, Santana do alfie, São Domingos do Prata</t>
+  </si>
+  <si>
+    <t>Rua Colatina 393, Industrial, João Monlevade</t>
   </si>
   <si>
     <t>Rua Santa Mônica 64, José Elói, João Monlevade</t>
   </si>
   <si>
+    <t>Rua Benedito Valadares 10 A, Doze de Março, Itabira</t>
+  </si>
+  <si>
     <t>Rua Acre 357 casa, Barro Branco, Itabira</t>
   </si>
   <si>
-    <t>Rua Ermantino Correia 96 Casa, São Veríssimo, Santa Bárbara</t>
-  </si>
-  <si>
-    <t>Monsenhor lelis 00 Casa, Santana do alfie, São Domingos do Prata</t>
+    <t>rua Prudente de Morais 45 casa, centro, Itambé do Mato Dentro</t>
+  </si>
+  <si>
+    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
+  </si>
+  <si>
+    <t>𝐑𝐮𝐚 𝐫𝐚𝐮𝐥 𝐡𝐨𝐬𝐤𝐞𝐧 34 𝐬𝐮𝐩𝐞𝐫𝐦𝐞𝐫𝐜𝐚𝐝𝐨 𝐭𝐫𝐞𝐯𝐨, 𝐒𝐚𝐨 𝐛𝐞𝐧𝐭𝐨, Santa Bárbara</t>
+  </si>
+  <si>
+    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
   </si>
   <si>
     <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
   </si>
   <si>
-    <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
-  </si>
-  <si>
-    <t>Rua Olga Krupp Silva 103 103, Vale da Serra, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Padre Pedro Domingues 266 loja, Centro, São Domingos do Prata</t>
-  </si>
-  <si>
-    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Platina 19 101, Santa Bárbara, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Barão de Cocais 1100 1100 Apartamento 402 bloco 04, Nova Esperança, João Monlevade</t>
-  </si>
-  <si>
-    <t>Paulo rolla 58, ceramica, São Domingos do Prata</t>
-  </si>
-  <si>
-    <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Caetés 133, Industrial, João Monlevade</t>
-  </si>
-  <si>
-    <t>Blusa Premium Ideal para Academia em Vários Cores e Estilos Confortáveis*1</t>
+    <t>Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1</t>
+  </si>
+  <si>
+    <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
+  </si>
+  <si>
+    <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
+  </si>
+  <si>
+    <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
+  </si>
+  <si>
+    <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
   </si>
   <si>
     <t>Jogo De Lençol 2 e 3 Peças premium 400 fios Solteiro Casal Queen King*1+Jogo De Lençol 2 e 3 Peças premium 400 fios Solteiro Casal Queen King*1</t>
   </si>
   <si>
+    <t>Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1</t>
+  </si>
+  <si>
     <t>Rastreador Chaveiro de Bagagem Mala PetAnti-Perda Mini Localizador Chaveiro GPS(Compatível com Android e iOS)*1</t>
   </si>
   <si>
-    <t>Kit 3 Calcinhas Borboleta VERMELHA PRETA BRANCA Fio Dental Sexy Regulagem Sensual Lingerie Feminina Tanga*1</t>
-  </si>
-  <si>
-    <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
+    <t>KINETX Fita Métrica De Aço Carbono De Alta Precisão 5M/7.5M/10M Trena Profissional Fluorescente Trava À Prova D'Água Sem Emaranhamento*1</t>
+  </si>
+  <si>
+    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
+  </si>
+  <si>
+    <t>Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1</t>
+  </si>
+  <si>
+    <t>Tênis Feminino Elegante Conforto Dia a Dia Versão Trend 2025*1</t>
+  </si>
+  <si>
+    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
   </si>
   <si>
     <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
-  </si>
-  <si>
-    <t>Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1</t>
-  </si>
-  <si>
-    <t>Placa Gua Sha Massagem Facial Pedra Anti Ruga Em Aço Inox - Skin Care*1</t>
-  </si>
-  <si>
-    <t>Carteira Masculina Couro Legitimo Slim Pequena Executiva de Bolso*1</t>
-  </si>
-  <si>
-    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
-  </si>
-  <si>
-    <t>Colar de camada dupla apresenta as letra do nome e um pingente em forma de coração, e é banhado a*1</t>
-  </si>
-  <si>
-    <t>Cinto Masculino de Couro Sintético com Fivela de Catraca – Elegância e Praticidade*1</t>
-  </si>
-  <si>
-    <t>Body Feminino Mula Manca com Gola Alta Moda Verão Praia*1</t>
-  </si>
-  <si>
-    <t>Calcinha de Emagrecimento / Cinta Modeladora / Roupa Íntima / Afina a Barriga Leggings Calça*1</t>
-  </si>
-  <si>
-    <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,11 +338,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -379,7 +392,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -411,9 +424,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -445,6 +476,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -620,11 +669,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -644,272 +693,272 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
@@ -921,15 +970,15 @@
         <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>45</v>
@@ -941,27 +990,7 @@
         <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_776161F9F613C836C26108D6AD0B636E49FA9099" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08AA4311-B6CE-4FD4-9241-1B3D3BADD104}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="96">
   <si>
     <t>AWB</t>
   </si>
@@ -45,263 +34,281 @@
     <t>Produto</t>
   </si>
   <si>
+    <t>6041726522534</t>
+  </si>
+  <si>
+    <t>3320022360871</t>
+  </si>
+  <si>
+    <t>3320019348079</t>
+  </si>
+  <si>
+    <t>3320096343566</t>
+  </si>
+  <si>
+    <t>3320090359776</t>
+  </si>
+  <si>
+    <t>3320009365112</t>
+  </si>
+  <si>
+    <t>3320038351075</t>
+  </si>
+  <si>
     <t>3320090345591</t>
   </si>
   <si>
-    <t>3320019348079</t>
-  </si>
-  <si>
-    <t>3320028356609</t>
+    <t>3320033358219</t>
+  </si>
+  <si>
+    <t>3320095353798</t>
+  </si>
+  <si>
+    <t>3320001366519</t>
+  </si>
+  <si>
+    <t>3320097350679</t>
+  </si>
+  <si>
+    <t>3320071350136</t>
+  </si>
+  <si>
+    <t>3320096358643</t>
+  </si>
+  <si>
+    <t>3320057350290</t>
   </si>
   <si>
     <t>3320065314168</t>
   </si>
   <si>
-    <t>3320033358219</t>
-  </si>
-  <si>
-    <t>3320090359776</t>
-  </si>
-  <si>
-    <t>3320072358688</t>
-  </si>
-  <si>
-    <t>3320057350290</t>
-  </si>
-  <si>
     <t>3320085334706</t>
   </si>
   <si>
-    <t>3320054347575</t>
-  </si>
-  <si>
-    <t>3320096343566</t>
-  </si>
-  <si>
     <t>3320022349122</t>
   </si>
   <si>
-    <t>3320038351075</t>
-  </si>
-  <si>
-    <t>3320009365112</t>
-  </si>
-  <si>
-    <t>3320022360871</t>
+    <t>3320041357597</t>
+  </si>
+  <si>
+    <t>6041726374040</t>
+  </si>
+  <si>
+    <t>(STB LOC) ALINE CRISTINA SANTOS</t>
+  </si>
+  <si>
+    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
+  </si>
+  <si>
+    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+  </si>
+  <si>
+    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
+  </si>
+  <si>
+    <t>(JML LOC) ROGER CARLOS BRAGA</t>
   </si>
   <si>
     <t>(STB LOC) CARLOS VINICIOS EFIRMIANDO</t>
   </si>
   <si>
-    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
-  </si>
-  <si>
-    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
-  </si>
-  <si>
-    <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
-  </si>
-  <si>
     <t>(JML INT) YURI ANTONIO - PRATA</t>
   </si>
   <si>
     <t>(JML LOC)TIAGO SALES MENDES</t>
   </si>
   <si>
-    <t>(JML INT) LUCAS SANTOS - ITABIRA</t>
-  </si>
-  <si>
-    <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
-  </si>
-  <si>
-    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
-  </si>
-  <si>
-    <t>(JML LOC) ROGER CARLOS BRAGA</t>
+    <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
+  </si>
+  <si>
+    <t>(JML INT)GETER HENRIQUE - ITABIRA</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Emily Cristina da Silva Zanella</t>
+  </si>
+  <si>
+    <t>diogo</t>
+  </si>
+  <si>
+    <t>milinha Vasconcellos</t>
+  </si>
+  <si>
+    <t>Kennedy Wander</t>
+  </si>
+  <si>
+    <t>eneluciafreitas</t>
+  </si>
+  <si>
+    <t>Alexandra Santos</t>
+  </si>
+  <si>
+    <t>kaw carvalho</t>
   </si>
   <si>
     <t>Rafaela Meireles Coutinho</t>
   </si>
   <si>
-    <t>milinha Vasconcellos</t>
-  </si>
-  <si>
-    <t>Eduarda</t>
-  </si>
-  <si>
-    <t>daniloluz20</t>
-  </si>
-  <si>
     <t>jc.yxr7</t>
   </si>
   <si>
-    <t>eneluciafreitas</t>
-  </si>
-  <si>
-    <t>Carolina Carvalho</t>
-  </si>
-  <si>
-    <t>Jane kelly</t>
-  </si>
-  <si>
-    <t>Luciano Almeida Gonçalves</t>
-  </si>
-  <si>
-    <t>Robson Gonçalves de Almeida</t>
-  </si>
-  <si>
-    <t>Kennedy Wander</t>
-  </si>
-  <si>
-    <t>Lari Lari</t>
-  </si>
-  <si>
-    <t>kaw carvalho</t>
-  </si>
-  <si>
-    <t>Alexandra Santos</t>
-  </si>
-  <si>
-    <t>diogo</t>
+    <t>elainecamposandra</t>
+  </si>
+  <si>
+    <t>Lorena Silva</t>
+  </si>
+  <si>
+    <t>bernardo reis</t>
+  </si>
+  <si>
+    <t>Giseli costa Espindola Gomes</t>
+  </si>
+  <si>
+    <t>+5531982629023</t>
+  </si>
+  <si>
+    <t>+5527981191289</t>
+  </si>
+  <si>
+    <t>+5531982151895</t>
+  </si>
+  <si>
+    <t>+5553191738884</t>
+  </si>
+  <si>
+    <t>+5531998675818</t>
+  </si>
+  <si>
+    <t>+5535998721133</t>
+  </si>
+  <si>
+    <t>+5553399944958</t>
   </si>
   <si>
     <t>+5531994061028</t>
   </si>
   <si>
-    <t>+5531982151895</t>
-  </si>
-  <si>
-    <t>+5531993769655</t>
-  </si>
-  <si>
-    <t>+5592982080755</t>
-  </si>
-  <si>
     <t>+5531971962410</t>
   </si>
   <si>
-    <t>+5531998675818</t>
-  </si>
-  <si>
-    <t>+5531992722136</t>
-  </si>
-  <si>
-    <t>+5531990708633</t>
-  </si>
-  <si>
-    <t>+5531999789232</t>
-  </si>
-  <si>
-    <t>+5531998320772</t>
-  </si>
-  <si>
-    <t>+5553191738884</t>
-  </si>
-  <si>
-    <t>+5531994361780</t>
-  </si>
-  <si>
-    <t>+5553399944958</t>
-  </si>
-  <si>
-    <t>+5535998721133</t>
-  </si>
-  <si>
-    <t>+5527981191289</t>
+    <t>+5531999068173</t>
+  </si>
+  <si>
+    <t>+5531986090083</t>
+  </si>
+  <si>
+    <t>+5531971549283</t>
+  </si>
+  <si>
+    <t>+5531999368116</t>
+  </si>
+  <si>
+    <t>rua izolina raimunda a silva, 145 -, garcia, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Colatina 393, Industrial, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
+  </si>
+  <si>
+    <t>𝐑𝐮𝐚 𝐫𝐚𝐮𝐥 𝐡𝐨𝐬𝐤𝐞𝐧 34 𝐬𝐮𝐩𝐞𝐫𝐦𝐞𝐫𝐜𝐚𝐝𝐨 𝐭𝐫𝐞𝐯𝐨, 𝐒𝐚𝐨 𝐛𝐞𝐧𝐭𝐨, Santa Bárbara</t>
   </si>
   <si>
     <t>Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara</t>
   </si>
   <si>
-    <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Caetés 133, Industrial, João Monlevade</t>
+    <t>Monsenhor lelis 00 Casa, Santana do alfie, São Domingos do Prata</t>
+  </si>
+  <si>
+    <t>Rua Santa Mônica 34 casa, José Elói, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Odorico Albuquerque 11 casa, Campestre I, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Ipê Roxo 147 casa, Jardim dos Ipês, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Benedito Valadares 10 A, Doze de Março, Itabira</t>
   </si>
   <si>
     <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
   </si>
   <si>
-    <t>Monsenhor lelis 00 Casa, Santana do alfie, São Domingos do Prata</t>
-  </si>
-  <si>
-    <t>Rua Colatina 393, Industrial, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Santa Mônica 64, José Elói, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Benedito Valadares 10 A, Doze de Março, Itabira</t>
-  </si>
-  <si>
     <t>Rua Acre 357 casa, Barro Branco, Itabira</t>
   </si>
   <si>
-    <t>rua Prudente de Morais 45 casa, centro, Itambé do Mato Dentro</t>
-  </si>
-  <si>
-    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
-  </si>
-  <si>
     <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
   </si>
   <si>
-    <t>𝐑𝐮𝐚 𝐫𝐚𝐮𝐥 𝐡𝐨𝐬𝐤𝐞𝐧 34 𝐬𝐮𝐩𝐞𝐫𝐦𝐞𝐫𝐜𝐚𝐝𝐨 𝐭𝐫𝐞𝐯𝐨, 𝐒𝐚𝐨 𝐛𝐞𝐧𝐭𝐨, Santa Bárbara</t>
-  </si>
-  <si>
-    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
+    <t>rua Francis Hime 397 casa do fundo, Irmãos Aleme, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
+  </si>
+  <si>
+    <t>DIVERSOS*1</t>
+  </si>
+  <si>
+    <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
+  </si>
+  <si>
+    <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
+  </si>
+  <si>
+    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
+  </si>
+  <si>
+    <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
+  </si>
+  <si>
+    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
+  </si>
+  <si>
+    <t>Tênis Feminino Elegante Conforto Dia a Dia Versão Trend 2025*1</t>
   </si>
   <si>
     <t>Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1</t>
   </si>
   <si>
-    <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
-  </si>
-  <si>
     <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
   </si>
   <si>
-    <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
-  </si>
-  <si>
-    <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
-  </si>
-  <si>
-    <t>Jogo De Lençol 2 e 3 Peças premium 400 fios Solteiro Casal Queen King*1+Jogo De Lençol 2 e 3 Peças premium 400 fios Solteiro Casal Queen King*1</t>
-  </si>
-  <si>
-    <t>Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1</t>
-  </si>
-  <si>
-    <t>Rastreador Chaveiro de Bagagem Mala PetAnti-Perda Mini Localizador Chaveiro GPS(Compatível com Android e iOS)*1</t>
-  </si>
-  <si>
-    <t>KINETX Fita Métrica De Aço Carbono De Alta Precisão 5M/7.5M/10M Trena Profissional Fluorescente Trava À Prova D'Água Sem Emaranhamento*1</t>
-  </si>
-  <si>
-    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
-  </si>
-  <si>
-    <t>Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1</t>
-  </si>
-  <si>
-    <t>Tênis Feminino Elegante Conforto Dia a Dia Versão Trend 2025*1</t>
-  </si>
-  <si>
-    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
-  </si>
-  <si>
-    <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
+    <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
+  </si>
+  <si>
+    <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
+  </si>
+  <si>
+    <t>TB Moda Kit Corrente Pulseira em Aço Inoxi Masculina/Feminina*1</t>
+  </si>
+  <si>
+    <t>Casaco Teddy Plus Size Feminino Longo Pelinho Com Capuz*1</t>
+  </si>
+  <si>
+    <t>****</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,19 +345,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -392,7 +391,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -424,27 +423,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -476,24 +457,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -669,11 +632,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,304 +656,362 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
         <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" t="s">
-        <v>89</v>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC83F2E1-F4A5-463C-B45E-537121EF0BA5}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="135">
   <si>
     <t>AWB</t>
   </si>
@@ -34,282 +45,407 @@
     <t>Produto</t>
   </si>
   <si>
+    <t>3320071350136</t>
+  </si>
+  <si>
+    <t>3320041357597</t>
+  </si>
+  <si>
+    <t>3320001366519</t>
+  </si>
+  <si>
+    <t>3320058358093</t>
+  </si>
+  <si>
+    <t>3320067346239</t>
+  </si>
+  <si>
+    <t>3320090359776</t>
+  </si>
+  <si>
+    <t>3320022360871</t>
+  </si>
+  <si>
+    <t>3320096358643</t>
+  </si>
+  <si>
+    <t>3320097350679</t>
+  </si>
+  <si>
+    <t>3320065314168</t>
+  </si>
+  <si>
+    <t>3320096343566</t>
+  </si>
+  <si>
+    <t>3320009365112</t>
+  </si>
+  <si>
     <t>6041726522534</t>
   </si>
   <si>
-    <t>3320022360871</t>
-  </si>
-  <si>
     <t>3320019348079</t>
   </si>
   <si>
-    <t>3320096343566</t>
-  </si>
-  <si>
-    <t>3320090359776</t>
-  </si>
-  <si>
-    <t>3320009365112</t>
-  </si>
-  <si>
     <t>3320038351075</t>
   </si>
   <si>
+    <t>3320022349122</t>
+  </si>
+  <si>
+    <t>3320095349691</t>
+  </si>
+  <si>
+    <t>6041726374040</t>
+  </si>
+  <si>
+    <t>3320073355871</t>
+  </si>
+  <si>
     <t>3320090345591</t>
   </si>
   <si>
-    <t>3320033358219</t>
+    <t>3320057350290</t>
+  </si>
+  <si>
+    <t>3320085334706</t>
   </si>
   <si>
     <t>3320095353798</t>
   </si>
   <si>
-    <t>3320001366519</t>
-  </si>
-  <si>
-    <t>3320097350679</t>
-  </si>
-  <si>
-    <t>3320071350136</t>
-  </si>
-  <si>
-    <t>3320096358643</t>
-  </si>
-  <si>
-    <t>3320057350290</t>
-  </si>
-  <si>
-    <t>3320065314168</t>
-  </si>
-  <si>
-    <t>3320085334706</t>
-  </si>
-  <si>
-    <t>3320022349122</t>
-  </si>
-  <si>
-    <t>3320041357597</t>
-  </si>
-  <si>
-    <t>6041726374040</t>
+    <t>(JML INT)GETER HENRIQUE - ITABIRA</t>
+  </si>
+  <si>
+    <t>(STB LOC) PAMELA LANA REZENDE</t>
+  </si>
+  <si>
+    <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
+  </si>
+  <si>
+    <t>(JML INT)WINDISON MAICON - ITABIRA</t>
+  </si>
+  <si>
+    <t>(STB LOC)JOÃO HILBERT DA SILVA</t>
+  </si>
+  <si>
+    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
+  </si>
+  <si>
+    <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
+  </si>
+  <si>
+    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
+  </si>
+  <si>
+    <t>(JML LOC) ROGER CARLOS BRAGA</t>
   </si>
   <si>
     <t>(STB LOC) ALINE CRISTINA SANTOS</t>
   </si>
   <si>
-    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
-  </si>
-  <si>
     <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
   </si>
   <si>
-    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
-  </si>
-  <si>
-    <t>(JML LOC) ROGER CARLOS BRAGA</t>
-  </si>
-  <si>
     <t>(STB LOC) CARLOS VINICIOS EFIRMIANDO</t>
   </si>
   <si>
-    <t>(JML INT) YURI ANTONIO - PRATA</t>
+    <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
+  </si>
+  <si>
+    <t>(STB LOC)DIOVANI WALISON DE ANDRADE</t>
+  </si>
+  <si>
+    <t>(JML INT) LUCAS SANTOS - ITABIRA</t>
+  </si>
+  <si>
+    <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
   </si>
   <si>
     <t>(JML LOC)TIAGO SALES MENDES</t>
   </si>
   <si>
-    <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
-  </si>
-  <si>
-    <t>(JML INT)GETER HENRIQUE - ITABIRA</t>
-  </si>
-  <si>
-    <t>N/A</t>
+    <t>Giseli costa Espindola Gomes</t>
+  </si>
+  <si>
+    <t>Jenifer Kelly</t>
+  </si>
+  <si>
+    <t>Lorena Silva</t>
+  </si>
+  <si>
+    <t>Ruth Vitoria</t>
+  </si>
+  <si>
+    <t>Mariana Silva</t>
+  </si>
+  <si>
+    <t>eneluciafreitas</t>
+  </si>
+  <si>
+    <t>diogo</t>
+  </si>
+  <si>
+    <t>bernardo reis</t>
+  </si>
+  <si>
+    <t>daniloluz20</t>
+  </si>
+  <si>
+    <t>Kennedy Wander</t>
+  </si>
+  <si>
+    <t>Alexandra Santos</t>
   </si>
   <si>
     <t>Emily Cristina da Silva Zanella</t>
   </si>
   <si>
-    <t>diogo</t>
-  </si>
-  <si>
     <t>milinha Vasconcellos</t>
   </si>
   <si>
-    <t>Kennedy Wander</t>
-  </si>
-  <si>
-    <t>eneluciafreitas</t>
-  </si>
-  <si>
-    <t>Alexandra Santos</t>
-  </si>
-  <si>
     <t>kaw carvalho</t>
   </si>
   <si>
+    <t>Lari Lari</t>
+  </si>
+  <si>
+    <t>Lali</t>
+  </si>
+  <si>
+    <t>Sara Cristina da Silva de Oliveira</t>
+  </si>
+  <si>
+    <t>Joice Mara do Carmo pinto marques</t>
+  </si>
+  <si>
     <t>Rafaela Meireles Coutinho</t>
   </si>
   <si>
-    <t>jc.yxr7</t>
+    <t>Jane kelly</t>
+  </si>
+  <si>
+    <t>Luciano Almeida Gonçalves</t>
   </si>
   <si>
     <t>elainecamposandra</t>
   </si>
   <si>
-    <t>Lorena Silva</t>
-  </si>
-  <si>
-    <t>bernardo reis</t>
-  </si>
-  <si>
-    <t>Giseli costa Espindola Gomes</t>
+    <t>+5531999368116</t>
+  </si>
+  <si>
+    <t>+5531995264171</t>
+  </si>
+  <si>
+    <t>+5531986090083</t>
+  </si>
+  <si>
+    <t>+5531987510691</t>
+  </si>
+  <si>
+    <t>+5531995050247</t>
+  </si>
+  <si>
+    <t>+5531998675818</t>
+  </si>
+  <si>
+    <t>+5527981191289</t>
+  </si>
+  <si>
+    <t>+5531971549283</t>
+  </si>
+  <si>
+    <t>+5592982080755</t>
+  </si>
+  <si>
+    <t>+5553191738884</t>
+  </si>
+  <si>
+    <t>+5535998721133</t>
   </si>
   <si>
     <t>+5531982629023</t>
   </si>
   <si>
-    <t>+5527981191289</t>
-  </si>
-  <si>
     <t>+5531982151895</t>
   </si>
   <si>
-    <t>+5553191738884</t>
-  </si>
-  <si>
-    <t>+5531998675818</t>
-  </si>
-  <si>
-    <t>+5535998721133</t>
-  </si>
-  <si>
     <t>+5553399944958</t>
   </si>
   <si>
+    <t>+5531994361780</t>
+  </si>
+  <si>
+    <t>+5531983648807</t>
+  </si>
+  <si>
+    <t>+5531995529037</t>
+  </si>
+  <si>
+    <t>+5531996862635</t>
+  </si>
+  <si>
     <t>+5531994061028</t>
   </si>
   <si>
-    <t>+5531971962410</t>
+    <t>+5531990708633</t>
+  </si>
+  <si>
+    <t>+5531999789232</t>
   </si>
   <si>
     <t>+5531999068173</t>
   </si>
   <si>
-    <t>+5531986090083</t>
-  </si>
-  <si>
-    <t>+5531971549283</t>
-  </si>
-  <si>
-    <t>+5531999368116</t>
+    <t>Rua Ipê Roxo 147 casa, Jardim dos Ipês, Itabira</t>
+  </si>
+  <si>
+    <t>rua Francis Hime 397 casa do fundo, Irmãos Aleme, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Afonso Arinos 33 casa, João XXIII, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Padre Teles 533 Casa Fundos, Vila São Geraldo, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Rua Colatina 393, Industrial, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Odorico Albuquerque 11 casa, Campestre I, Itabira</t>
+  </si>
+  <si>
+    <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
   </si>
   <si>
     <t>rua izolina raimunda a silva, 145 -, garcia, Barão de Cocais</t>
   </si>
   <si>
-    <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
-  </si>
-  <si>
     <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
   </si>
   <si>
-    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Colatina 393, Industrial, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
-  </si>
-  <si>
     <t>𝐑𝐮𝐚 𝐫𝐚𝐮𝐥 𝐡𝐨𝐬𝐤𝐞𝐧 34 𝐬𝐮𝐩𝐞𝐫𝐦𝐞𝐫𝐜𝐚𝐝𝐨 𝐭𝐫𝐞𝐯𝐨, 𝐒𝐚𝐨 𝐛𝐞𝐧𝐭𝐨, Santa Bárbara</t>
   </si>
   <si>
+    <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
+  </si>
+  <si>
+    <t>Rua Osvaldo Bastos Werneck 207 Casa, Centro, Sem-Peixe</t>
+  </si>
+  <si>
+    <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Olegário Maciel 69 casa, Lagoa, Barão de Cocais</t>
+  </si>
+  <si>
     <t>Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara</t>
   </si>
   <si>
-    <t>Monsenhor lelis 00 Casa, Santana do alfie, São Domingos do Prata</t>
+    <t>Rua Benedito Valadares 10 A, Doze de Março, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Acre 357 casa, Barro Branco, Itabira</t>
   </si>
   <si>
     <t>Rua Santa Mônica 34 casa, José Elói, João Monlevade</t>
   </si>
   <si>
-    <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Odorico Albuquerque 11 casa, Campestre I, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Ipê Roxo 147 casa, Jardim dos Ipês, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Benedito Valadares 10 A, Doze de Março, Itabira</t>
-  </si>
-  <si>
-    <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Acre 357 casa, Barro Branco, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
-  </si>
-  <si>
-    <t>rua Francis Hime 397 casa do fundo, Irmãos Aleme, Barão de Cocais</t>
-  </si>
-  <si>
-    <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
+    <t>Casaco Teddy Plus Size Feminino Longo Pelinho Com Capuz*1</t>
+  </si>
+  <si>
+    <t>Escova de Limpeza Esfregão 3 Em 1 vassoura rodo chão cozinha Banheiro*1</t>
+  </si>
+  <si>
+    <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
+  </si>
+  <si>
+    <t>Projetor HY300 Portátil Smart Android 11 4K Ultra HD Wifi Bluetooth Cinema em Casa com Alto Falante*1</t>
+  </si>
+  <si>
+    <t>Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1+Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1</t>
+  </si>
+  <si>
+    <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
+  </si>
+  <si>
+    <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
+  </si>
+  <si>
+    <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
+  </si>
+  <si>
+    <t>TB Moda Kit Corrente Pulseira em Aço Inoxi Masculina/Feminina*1</t>
+  </si>
+  <si>
+    <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
+  </si>
+  <si>
+    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
+  </si>
+  <si>
+    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
   </si>
   <si>
     <t>DIVERSOS*1</t>
   </si>
   <si>
-    <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
-  </si>
-  <si>
     <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
   </si>
   <si>
-    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
-  </si>
-  <si>
-    <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
-  </si>
-  <si>
-    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
-  </si>
-  <si>
     <t>Tênis Feminino Elegante Conforto Dia a Dia Versão Trend 2025*1</t>
   </si>
   <si>
+    <t>Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1</t>
+  </si>
+  <si>
+    <t>Colar semi joia arvore da vida corrente veneziana verniz italiano*1</t>
+  </si>
+  <si>
+    <t>Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1</t>
+  </si>
+  <si>
+    <t>Conjunto Feminino Inverno Plush. Tamanhos: P ao Plus Size - Com zíper, capuz e bolso. Agasalho quentinho, liso e básico moda curve*1</t>
+  </si>
+  <si>
     <t>Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1</t>
   </si>
   <si>
-    <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
+    <t>Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1</t>
+  </si>
+  <si>
+    <t>Rastreador Chaveiro de Bagagem Mala PetAnti-Perda Mini Localizador Chaveiro GPS(Compatível com Android e iOS)*1</t>
   </si>
   <si>
     <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
-  </si>
-  <si>
-    <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
-  </si>
-  <si>
-    <t>TB Moda Kit Corrente Pulseira em Aço Inoxi Masculina/Feminina*1</t>
-  </si>
-  <si>
-    <t>Casaco Teddy Plus Size Feminino Longo Pelinho Com Capuz*1</t>
-  </si>
-  <si>
-    <t>****</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -337,19 +473,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -391,7 +536,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -423,9 +568,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -457,6 +620,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -632,11 +813,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -656,147 +837,147 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -804,215 +985,318 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="B14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
-      </c>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" t="s">
+        <v>134</v>
+      </c>
+      <c r="N24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC83F2E1-F4A5-463C-B45E-537121EF0BA5}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48B0DC9-4289-451B-8C6A-9E5369B7AF62}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="3" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <pivotCaches>
+    <pivotCache cacheId="192" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="115">
   <si>
     <t>AWB</t>
   </si>
@@ -66,12 +71,6 @@
     <t>3320022360871</t>
   </si>
   <si>
-    <t>3320096358643</t>
-  </si>
-  <si>
-    <t>3320097350679</t>
-  </si>
-  <si>
     <t>3320065314168</t>
   </si>
   <si>
@@ -87,9 +86,6 @@
     <t>3320019348079</t>
   </si>
   <si>
-    <t>3320038351075</t>
-  </si>
-  <si>
     <t>3320022349122</t>
   </si>
   <si>
@@ -108,12 +104,6 @@
     <t>3320057350290</t>
   </si>
   <si>
-    <t>3320085334706</t>
-  </si>
-  <si>
-    <t>3320095353798</t>
-  </si>
-  <si>
     <t>(JML INT)GETER HENRIQUE - ITABIRA</t>
   </si>
   <si>
@@ -159,12 +149,6 @@
     <t>(JML INT) LUCAS SANTOS - ITABIRA</t>
   </si>
   <si>
-    <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
-  </si>
-  <si>
-    <t>(JML LOC)TIAGO SALES MENDES</t>
-  </si>
-  <si>
     <t>Giseli costa Espindola Gomes</t>
   </si>
   <si>
@@ -186,9 +170,6 @@
     <t>diogo</t>
   </si>
   <si>
-    <t>bernardo reis</t>
-  </si>
-  <si>
     <t>daniloluz20</t>
   </si>
   <si>
@@ -204,9 +185,6 @@
     <t>milinha Vasconcellos</t>
   </si>
   <si>
-    <t>kaw carvalho</t>
-  </si>
-  <si>
     <t>Lari Lari</t>
   </si>
   <si>
@@ -225,12 +203,6 @@
     <t>Jane kelly</t>
   </si>
   <si>
-    <t>Luciano Almeida Gonçalves</t>
-  </si>
-  <si>
-    <t>elainecamposandra</t>
-  </si>
-  <si>
     <t>+5531999368116</t>
   </si>
   <si>
@@ -252,9 +224,6 @@
     <t>+5527981191289</t>
   </si>
   <si>
-    <t>+5531971549283</t>
-  </si>
-  <si>
     <t>+5592982080755</t>
   </si>
   <si>
@@ -270,9 +239,6 @@
     <t>+5531982151895</t>
   </si>
   <si>
-    <t>+5553399944958</t>
-  </si>
-  <si>
     <t>+5531994361780</t>
   </si>
   <si>
@@ -291,12 +257,6 @@
     <t>+5531990708633</t>
   </si>
   <si>
-    <t>+5531999789232</t>
-  </si>
-  <si>
-    <t>+5531999068173</t>
-  </si>
-  <si>
     <t>Rua Ipê Roxo 147 casa, Jardim dos Ipês, Itabira</t>
   </si>
   <si>
@@ -318,9 +278,6 @@
     <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
   </si>
   <si>
-    <t>Rua Odorico Albuquerque 11 casa, Campestre I, Itabira</t>
-  </si>
-  <si>
     <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
   </si>
   <si>
@@ -336,9 +293,6 @@
     <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
   </si>
   <si>
-    <t>𝐑𝐮𝐚 𝐫𝐚𝐮𝐥 𝐡𝐨𝐬𝐤𝐞𝐧 34 𝐬𝐮𝐩𝐞𝐫𝐦𝐞𝐫𝐜𝐚𝐝𝐨 𝐭𝐫𝐞𝐯𝐨, 𝐒𝐚𝐨 𝐛𝐞𝐧𝐭𝐨, Santa Bárbara</t>
-  </si>
-  <si>
     <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
   </si>
   <si>
@@ -357,12 +311,6 @@
     <t>Rua Benedito Valadares 10 A, Doze de Março, Itabira</t>
   </si>
   <si>
-    <t>Rua Acre 357 casa, Barro Branco, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Santa Mônica 34 casa, José Elói, João Monlevade</t>
-  </si>
-  <si>
     <t>Casaco Teddy Plus Size Feminino Longo Pelinho Com Capuz*1</t>
   </si>
   <si>
@@ -384,12 +332,6 @@
     <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
   </si>
   <si>
-    <t>Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1</t>
-  </si>
-  <si>
-    <t>TB Moda Kit Corrente Pulseira em Aço Inoxi Masculina/Feminina*1</t>
-  </si>
-  <si>
     <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
   </si>
   <si>
@@ -405,9 +347,6 @@
     <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
   </si>
   <si>
-    <t>Tênis Feminino Elegante Conforto Dia a Dia Versão Trend 2025*1</t>
-  </si>
-  <si>
     <t>Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1</t>
   </si>
   <si>
@@ -426,17 +365,23 @@
     <t>Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1</t>
   </si>
   <si>
-    <t>Rastreador Chaveiro de Bagagem Mala PetAnti-Perda Mini Localizador Chaveiro GPS(Compatível com Android e iOS)*1</t>
-  </si>
-  <si>
-    <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>MOTORISTAS</t>
+  </si>
+  <si>
+    <t>QTD</t>
+  </si>
+  <si>
+    <t>ACAREAÇÕES EM ABERTO IMILE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,13 +397,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="22"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -473,9 +431,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,6 +455,353 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="digux" refreshedDate="46134.780410300926" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="24" xr:uid="{2D83F3AD-FF8C-46EA-A6A9-B5CA6F4E70F6}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F1048576" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="AWB" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Motorista" numFmtId="0">
+      <sharedItems containsBlank="1" count="18">
+        <s v="(JML INT)GETER HENRIQUE - ITABIRA"/>
+        <s v="(STB LOC) PAMELA LANA REZENDE"/>
+        <s v="(JML INT)WENDERSON ARAUJO - ITABIRA"/>
+        <s v="(JML INT)WINDISON MAICON - ITABIRA"/>
+        <s v="(STB LOC)JOÃO HILBERT DA SILVA"/>
+        <s v="(JML LOC) LUCAS FELIPE GOMES DA SILVA"/>
+        <s v="(JML LOC) RENNER DIEGO DE CARVALHO"/>
+        <s v="(JML INT) FRANCISMAR LIMA- BOM JESUS"/>
+        <s v="(JML LOC) ROGER CARLOS BRAGA"/>
+        <s v="(STB LOC) ALINE CRISTINA SANTOS"/>
+        <s v="(JML LOC) JOÃO PAULO BICALHO MARTINS"/>
+        <s v="(STB LOC) CARLOS VINICIOS EFIRMIANDO"/>
+        <s v="(JML INT) PARLLON MATOS - ALVINOPOLIS"/>
+        <s v="(STB LOC)DIOVANI WALISON DE ANDRADE"/>
+        <s v="(JML INT) LUCAS SANTOS - ITABIRA"/>
+        <s v="(JML INT) SERGIO DE ALMEIDA - ROÇA"/>
+        <s v="(JML LOC)TIAGO SALES MENDES"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Nome" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Telefone" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Endereco" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Produto" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="24">
+  <r>
+    <s v="3320071350136"/>
+    <x v="0"/>
+    <s v="Giseli costa Espindola Gomes"/>
+    <s v="+5531999368116"/>
+    <s v="Rua Ipê Roxo 147 casa, Jardim dos Ipês, Itabira"/>
+    <s v="Casaco Teddy Plus Size Feminino Longo Pelinho Com Capuz*1"/>
+  </r>
+  <r>
+    <s v="3320041357597"/>
+    <x v="1"/>
+    <s v="Jenifer Kelly"/>
+    <s v="+5531995264171"/>
+    <s v="rua Francis Hime 397 casa do fundo, Irmãos Aleme, Barão de Cocais"/>
+    <s v="Escova de Limpeza Esfregão 3 Em 1 vassoura rodo chão cozinha Banheiro*1"/>
+  </r>
+  <r>
+    <s v="3320001366519"/>
+    <x v="2"/>
+    <s v="Lorena Silva"/>
+    <s v="+5531986090083"/>
+    <s v="Rua Maurílio Martins de Souza 43, Fênix, Itabira"/>
+    <s v="Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2"/>
+  </r>
+  <r>
+    <s v="3320058358093"/>
+    <x v="3"/>
+    <s v="Ruth Vitoria"/>
+    <s v="+5531987510691"/>
+    <s v="Rua Afonso Arinos 33 casa, João XXIII, Itabira"/>
+    <s v="Projetor HY300 Portátil Smart Android 11 4K Ultra HD Wifi Bluetooth Cinema em Casa com Alto Falante*1"/>
+  </r>
+  <r>
+    <s v="3320067346239"/>
+    <x v="4"/>
+    <s v="Mariana Silva"/>
+    <s v="+5531995050247"/>
+    <s v="Rua Padre Teles 533 Casa Fundos, Vila São Geraldo, Barão de Cocais"/>
+    <s v="Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1+Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1"/>
+  </r>
+  <r>
+    <s v="3320090359776"/>
+    <x v="5"/>
+    <s v="eneluciafreitas"/>
+    <s v="+5531998675818"/>
+    <s v="Rua Colatina 393, Industrial, João Monlevade"/>
+    <s v="Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1"/>
+  </r>
+  <r>
+    <s v="3320022360871"/>
+    <x v="5"/>
+    <s v="diogo"/>
+    <s v="+5527981191289"/>
+    <s v="Rua Caetés 145 Casa, Industrial, João Monlevade"/>
+    <s v="Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1"/>
+  </r>
+  <r>
+    <s v="3320096358643"/>
+    <x v="2"/>
+    <s v="bernardo reis"/>
+    <s v="+5531971549283"/>
+    <s v="Rua Odorico Albuquerque 11 casa, Campestre I, Itabira"/>
+    <s v="Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1"/>
+  </r>
+  <r>
+    <s v="3320097350679"/>
+    <x v="2"/>
+    <s v="bernardo reis"/>
+    <s v="+5531971549283"/>
+    <s v="Rua Odorico Albuquerque 11 casa, Campestre I, Itabira"/>
+    <s v="TB Moda Kit Corrente Pulseira em Aço Inoxi Masculina/Feminina*1"/>
+  </r>
+  <r>
+    <s v="3320065314168"/>
+    <x v="6"/>
+    <s v="daniloluz20"/>
+    <s v="+5592982080755"/>
+    <s v="Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade"/>
+    <s v="Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1"/>
+  </r>
+  <r>
+    <s v="3320096343566"/>
+    <x v="7"/>
+    <s v="Kennedy Wander"/>
+    <s v="+5553191738884"/>
+    <s v="Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade"/>
+    <s v="Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1"/>
+  </r>
+  <r>
+    <s v="3320009365112"/>
+    <x v="8"/>
+    <s v="Alexandra Santos"/>
+    <s v="+5535998721133"/>
+    <s v="Rua Jasmim 44 Casa, Vila Tanque, João Monlevade"/>
+    <s v="Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1"/>
+  </r>
+  <r>
+    <s v="6041726522534"/>
+    <x v="9"/>
+    <s v="Emily Cristina da Silva Zanella"/>
+    <s v="+5531982629023"/>
+    <s v="rua izolina raimunda a silva, 145 -, garcia, Barão de Cocais"/>
+    <s v="DIVERSOS*1"/>
+  </r>
+  <r>
+    <s v="3320019348079"/>
+    <x v="10"/>
+    <s v="milinha Vasconcellos"/>
+    <s v="+5531982151895"/>
+    <s v="Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade"/>
+    <s v="Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1"/>
+  </r>
+  <r>
+    <s v="3320038351075"/>
+    <x v="11"/>
+    <s v="kaw carvalho"/>
+    <s v="+5553399944958"/>
+    <s v="𝐑𝐮𝐚 𝐫𝐚𝐮𝐥 𝐡𝐨𝐬𝐤𝐞𝐧 34 𝐬𝐮𝐩𝐞𝐫𝐦𝐞𝐫𝐜𝐚𝐝𝐨 𝐭𝐫𝐞𝐯𝐨, 𝐒𝐚𝐨 𝐛𝐞𝐧𝐭𝐨, Santa Bárbara"/>
+    <s v="Tênis Feminino Elegante Conforto Dia a Dia Versão Trend 2025*1"/>
+  </r>
+  <r>
+    <s v="3320022349122"/>
+    <x v="10"/>
+    <s v="Lari Lari"/>
+    <s v="+5531994361780"/>
+    <s v="Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo"/>
+    <s v="Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1"/>
+  </r>
+  <r>
+    <s v="3320095349691"/>
+    <x v="12"/>
+    <s v="Lali"/>
+    <s v="+5531983648807"/>
+    <s v="Rua Osvaldo Bastos Werneck 207 Casa, Centro, Sem-Peixe"/>
+    <s v="Colar semi joia arvore da vida corrente veneziana verniz italiano*1"/>
+  </r>
+  <r>
+    <s v="6041726374040"/>
+    <x v="10"/>
+    <s v="Sara Cristina da Silva de Oliveira"/>
+    <s v="+5531995529037"/>
+    <s v="Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade"/>
+    <s v="Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1"/>
+  </r>
+  <r>
+    <s v="3320073355871"/>
+    <x v="13"/>
+    <s v="Joice Mara do Carmo pinto marques"/>
+    <s v="+5531996862635"/>
+    <s v="Rua Olegário Maciel 69 casa, Lagoa, Barão de Cocais"/>
+    <s v="Conjunto Feminino Inverno Plush. Tamanhos: P ao Plus Size - Com zíper, capuz e bolso. Agasalho quentinho, liso e básico moda curve*1"/>
+  </r>
+  <r>
+    <s v="3320090345591"/>
+    <x v="11"/>
+    <s v="Rafaela Meireles Coutinho"/>
+    <s v="+5531994061028"/>
+    <s v="Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara"/>
+    <s v="Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1"/>
+  </r>
+  <r>
+    <s v="3320057350290"/>
+    <x v="14"/>
+    <s v="Jane kelly"/>
+    <s v="+5531990708633"/>
+    <s v="Rua Benedito Valadares 10 A, Doze de Março, Itabira"/>
+    <s v="Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1"/>
+  </r>
+  <r>
+    <s v="3320085334706"/>
+    <x v="15"/>
+    <s v="Luciano Almeida Gonçalves"/>
+    <s v="+5531999789232"/>
+    <s v="Rua Acre 357 casa, Barro Branco, Itabira"/>
+    <s v="Rastreador Chaveiro de Bagagem Mala PetAnti-Perda Mini Localizador Chaveiro GPS(Compatível com Android e iOS)*1"/>
+  </r>
+  <r>
+    <s v="3320095353798"/>
+    <x v="16"/>
+    <s v="elainecamposandra"/>
+    <s v="+5531999068173"/>
+    <s v="Rua Santa Mônica 34 casa, José Elói, João Monlevade"/>
+    <s v="Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1"/>
+  </r>
+  <r>
+    <m/>
+    <x v="17"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E00AE1C-2C32-4684-AA5E-103AD6B96447}" name="Tabela dinâmica42" cacheId="192" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MOTORISTAS">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="19">
+        <item h="1" x="7"/>
+        <item h="1" x="14"/>
+        <item h="1" x="12"/>
+        <item h="1" x="15"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="16"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item h="1" x="17"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="QTD" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleDark2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88682BFF-45CC-4F65-87CF-0204F987928D}" name="Tabela1" displayName="Tabela1" ref="A1:F2" totalsRowShown="0">
+  <autoFilter ref="A1:F2" xr:uid="{88682BFF-45CC-4F65-87CF-0204F987928D}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{0EBAE740-7BC6-403C-BB9E-41DE0548C3FA}" name="AWB"/>
+    <tableColumn id="2" xr3:uid="{196AD421-FDEF-428D-8EE8-30DD6C961E5B}" name="Motorista"/>
+    <tableColumn id="3" xr3:uid="{56825D65-48F8-4F47-BA85-CDAD6E8605EA}" name="Nome"/>
+    <tableColumn id="4" xr3:uid="{4E9EE87F-F806-45BF-8459-1C60C3A68CE2}" name="Telefone"/>
+    <tableColumn id="5" xr3:uid="{73F33F7D-C27B-4BB4-8498-4EBCE8531AB9}" name="Endereco"/>
+    <tableColumn id="6" xr3:uid="{660BA362-4676-4D61-B20D-EDD96B75D755}" name="Produto"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -813,9 +1124,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB946E88-CA76-406C-B1E6-F13BCD3ED444}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -839,22 +1156,154 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5B3F5F-991A-4DB8-A76A-24914CB92237}">
+  <dimension ref="A2:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="5"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="2">
         <v>6</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -862,19 +1311,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -882,19 +1331,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -902,19 +1351,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F5" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -922,19 +1371,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -942,19 +1391,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -962,19 +1411,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -982,19 +1431,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1005,16 +1454,16 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F10" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1022,39 +1471,39 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>99</v>
-      </c>
-      <c r="F12" t="s">
-        <v>122</v>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1062,19 +1511,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1082,19 +1531,19 @@
         <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1102,19 +1551,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1122,181 +1571,80 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
         <v>110</v>
       </c>
-      <c r="F23" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" t="s">
-        <v>134</v>
-      </c>
-      <c r="N24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48B0DC9-4289-451B-8C6A-9E5369B7AF62}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{793E6665-1C4F-4CB4-92D1-AC51DCE8A7D4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="192" r:id="rId4"/>
+    <pivotCache cacheId="193" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E00AE1C-2C32-4684-AA5E-103AD6B96447}" name="Tabela dinâmica42" cacheId="192" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MOTORISTAS">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E00AE1C-2C32-4684-AA5E-103AD6B96447}" name="Tabela dinâmica42" cacheId="193" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MOTORISTAS">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField dataField="1" showAll="0"/>
@@ -1264,6 +1264,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -8,19 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{793E6665-1C4F-4CB4-92D1-AC51DCE8A7D4}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D658B33-01BA-437E-BE34-1D5A79754D36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha2" sheetId="3" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <pivotCaches>
-    <pivotCache cacheId="193" r:id="rId4"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -30,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
   <si>
     <t>AWB</t>
   </si>
@@ -363,25 +358,13 @@
   </si>
   <si>
     <t>Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1</t>
-  </si>
-  <si>
-    <t>Total Geral</t>
-  </si>
-  <si>
-    <t>MOTORISTAS</t>
-  </si>
-  <si>
-    <t>QTD</t>
-  </si>
-  <si>
-    <t>ACAREAÇÕES EM ABERTO IMILE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,26 +380,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="22"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -431,15 +401,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,353 +419,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="digux" refreshedDate="46134.780410300926" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="24" xr:uid="{2D83F3AD-FF8C-46EA-A6A9-B5CA6F4E70F6}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F1048576" sheet="Sheet1"/>
-  </cacheSource>
-  <cacheFields count="6">
-    <cacheField name="AWB" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="Motorista" numFmtId="0">
-      <sharedItems containsBlank="1" count="18">
-        <s v="(JML INT)GETER HENRIQUE - ITABIRA"/>
-        <s v="(STB LOC) PAMELA LANA REZENDE"/>
-        <s v="(JML INT)WENDERSON ARAUJO - ITABIRA"/>
-        <s v="(JML INT)WINDISON MAICON - ITABIRA"/>
-        <s v="(STB LOC)JOÃO HILBERT DA SILVA"/>
-        <s v="(JML LOC) LUCAS FELIPE GOMES DA SILVA"/>
-        <s v="(JML LOC) RENNER DIEGO DE CARVALHO"/>
-        <s v="(JML INT) FRANCISMAR LIMA- BOM JESUS"/>
-        <s v="(JML LOC) ROGER CARLOS BRAGA"/>
-        <s v="(STB LOC) ALINE CRISTINA SANTOS"/>
-        <s v="(JML LOC) JOÃO PAULO BICALHO MARTINS"/>
-        <s v="(STB LOC) CARLOS VINICIOS EFIRMIANDO"/>
-        <s v="(JML INT) PARLLON MATOS - ALVINOPOLIS"/>
-        <s v="(STB LOC)DIOVANI WALISON DE ANDRADE"/>
-        <s v="(JML INT) LUCAS SANTOS - ITABIRA"/>
-        <s v="(JML INT) SERGIO DE ALMEIDA - ROÇA"/>
-        <s v="(JML LOC)TIAGO SALES MENDES"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Nome" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="Telefone" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="Endereco" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-    <cacheField name="Produto" numFmtId="0">
-      <sharedItems containsBlank="1"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="24">
-  <r>
-    <s v="3320071350136"/>
-    <x v="0"/>
-    <s v="Giseli costa Espindola Gomes"/>
-    <s v="+5531999368116"/>
-    <s v="Rua Ipê Roxo 147 casa, Jardim dos Ipês, Itabira"/>
-    <s v="Casaco Teddy Plus Size Feminino Longo Pelinho Com Capuz*1"/>
-  </r>
-  <r>
-    <s v="3320041357597"/>
-    <x v="1"/>
-    <s v="Jenifer Kelly"/>
-    <s v="+5531995264171"/>
-    <s v="rua Francis Hime 397 casa do fundo, Irmãos Aleme, Barão de Cocais"/>
-    <s v="Escova de Limpeza Esfregão 3 Em 1 vassoura rodo chão cozinha Banheiro*1"/>
-  </r>
-  <r>
-    <s v="3320001366519"/>
-    <x v="2"/>
-    <s v="Lorena Silva"/>
-    <s v="+5531986090083"/>
-    <s v="Rua Maurílio Martins de Souza 43, Fênix, Itabira"/>
-    <s v="Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2"/>
-  </r>
-  <r>
-    <s v="3320058358093"/>
-    <x v="3"/>
-    <s v="Ruth Vitoria"/>
-    <s v="+5531987510691"/>
-    <s v="Rua Afonso Arinos 33 casa, João XXIII, Itabira"/>
-    <s v="Projetor HY300 Portátil Smart Android 11 4K Ultra HD Wifi Bluetooth Cinema em Casa com Alto Falante*1"/>
-  </r>
-  <r>
-    <s v="3320067346239"/>
-    <x v="4"/>
-    <s v="Mariana Silva"/>
-    <s v="+5531995050247"/>
-    <s v="Rua Padre Teles 533 Casa Fundos, Vila São Geraldo, Barão de Cocais"/>
-    <s v="Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1+Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1"/>
-  </r>
-  <r>
-    <s v="3320090359776"/>
-    <x v="5"/>
-    <s v="eneluciafreitas"/>
-    <s v="+5531998675818"/>
-    <s v="Rua Colatina 393, Industrial, João Monlevade"/>
-    <s v="Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1"/>
-  </r>
-  <r>
-    <s v="3320022360871"/>
-    <x v="5"/>
-    <s v="diogo"/>
-    <s v="+5527981191289"/>
-    <s v="Rua Caetés 145 Casa, Industrial, João Monlevade"/>
-    <s v="Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1"/>
-  </r>
-  <r>
-    <s v="3320096358643"/>
-    <x v="2"/>
-    <s v="bernardo reis"/>
-    <s v="+5531971549283"/>
-    <s v="Rua Odorico Albuquerque 11 casa, Campestre I, Itabira"/>
-    <s v="Kit Carregador De iPhone Fonte com Cabo Carregamento Rápido 1m PD 20w*1"/>
-  </r>
-  <r>
-    <s v="3320097350679"/>
-    <x v="2"/>
-    <s v="bernardo reis"/>
-    <s v="+5531971549283"/>
-    <s v="Rua Odorico Albuquerque 11 casa, Campestre I, Itabira"/>
-    <s v="TB Moda Kit Corrente Pulseira em Aço Inoxi Masculina/Feminina*1"/>
-  </r>
-  <r>
-    <s v="3320065314168"/>
-    <x v="6"/>
-    <s v="daniloluz20"/>
-    <s v="+5592982080755"/>
-    <s v="Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade"/>
-    <s v="Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1"/>
-  </r>
-  <r>
-    <s v="3320096343566"/>
-    <x v="7"/>
-    <s v="Kennedy Wander"/>
-    <s v="+5553191738884"/>
-    <s v="Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade"/>
-    <s v="Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1"/>
-  </r>
-  <r>
-    <s v="3320009365112"/>
-    <x v="8"/>
-    <s v="Alexandra Santos"/>
-    <s v="+5535998721133"/>
-    <s v="Rua Jasmim 44 Casa, Vila Tanque, João Monlevade"/>
-    <s v="Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1"/>
-  </r>
-  <r>
-    <s v="6041726522534"/>
-    <x v="9"/>
-    <s v="Emily Cristina da Silva Zanella"/>
-    <s v="+5531982629023"/>
-    <s v="rua izolina raimunda a silva, 145 -, garcia, Barão de Cocais"/>
-    <s v="DIVERSOS*1"/>
-  </r>
-  <r>
-    <s v="3320019348079"/>
-    <x v="10"/>
-    <s v="milinha Vasconcellos"/>
-    <s v="+5531982151895"/>
-    <s v="Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade"/>
-    <s v="Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1"/>
-  </r>
-  <r>
-    <s v="3320038351075"/>
-    <x v="11"/>
-    <s v="kaw carvalho"/>
-    <s v="+5553399944958"/>
-    <s v="𝐑𝐮𝐚 𝐫𝐚𝐮𝐥 𝐡𝐨𝐬𝐤𝐞𝐧 34 𝐬𝐮𝐩𝐞𝐫𝐦𝐞𝐫𝐜𝐚𝐝𝐨 𝐭𝐫𝐞𝐯𝐨, 𝐒𝐚𝐨 𝐛𝐞𝐧𝐭𝐨, Santa Bárbara"/>
-    <s v="Tênis Feminino Elegante Conforto Dia a Dia Versão Trend 2025*1"/>
-  </r>
-  <r>
-    <s v="3320022349122"/>
-    <x v="10"/>
-    <s v="Lari Lari"/>
-    <s v="+5531994361780"/>
-    <s v="Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo"/>
-    <s v="Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1"/>
-  </r>
-  <r>
-    <s v="3320095349691"/>
-    <x v="12"/>
-    <s v="Lali"/>
-    <s v="+5531983648807"/>
-    <s v="Rua Osvaldo Bastos Werneck 207 Casa, Centro, Sem-Peixe"/>
-    <s v="Colar semi joia arvore da vida corrente veneziana verniz italiano*1"/>
-  </r>
-  <r>
-    <s v="6041726374040"/>
-    <x v="10"/>
-    <s v="Sara Cristina da Silva de Oliveira"/>
-    <s v="+5531995529037"/>
-    <s v="Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade"/>
-    <s v="Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1"/>
-  </r>
-  <r>
-    <s v="3320073355871"/>
-    <x v="13"/>
-    <s v="Joice Mara do Carmo pinto marques"/>
-    <s v="+5531996862635"/>
-    <s v="Rua Olegário Maciel 69 casa, Lagoa, Barão de Cocais"/>
-    <s v="Conjunto Feminino Inverno Plush. Tamanhos: P ao Plus Size - Com zíper, capuz e bolso. Agasalho quentinho, liso e básico moda curve*1"/>
-  </r>
-  <r>
-    <s v="3320090345591"/>
-    <x v="11"/>
-    <s v="Rafaela Meireles Coutinho"/>
-    <s v="+5531994061028"/>
-    <s v="Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara"/>
-    <s v="Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1"/>
-  </r>
-  <r>
-    <s v="3320057350290"/>
-    <x v="14"/>
-    <s v="Jane kelly"/>
-    <s v="+5531990708633"/>
-    <s v="Rua Benedito Valadares 10 A, Doze de Março, Itabira"/>
-    <s v="Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1"/>
-  </r>
-  <r>
-    <s v="3320085334706"/>
-    <x v="15"/>
-    <s v="Luciano Almeida Gonçalves"/>
-    <s v="+5531999789232"/>
-    <s v="Rua Acre 357 casa, Barro Branco, Itabira"/>
-    <s v="Rastreador Chaveiro de Bagagem Mala PetAnti-Perda Mini Localizador Chaveiro GPS(Compatível com Android e iOS)*1"/>
-  </r>
-  <r>
-    <s v="3320095353798"/>
-    <x v="16"/>
-    <s v="elainecamposandra"/>
-    <s v="+5531999068173"/>
-    <s v="Rua Santa Mônica 34 casa, José Elói, João Monlevade"/>
-    <s v="Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1"/>
-  </r>
-  <r>
-    <m/>
-    <x v="17"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E00AE1C-2C32-4684-AA5E-103AD6B96447}" name="Tabela dinâmica42" cacheId="193" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="MOTORISTAS">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="6">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="19">
-        <item h="1" x="7"/>
-        <item h="1" x="14"/>
-        <item h="1" x="12"/>
-        <item h="1" x="15"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="16"/>
-        <item x="9"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item h="1" x="17"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="QTD" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleDark2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88682BFF-45CC-4F65-87CF-0204F987928D}" name="Tabela1" displayName="Tabela1" ref="A1:F2" totalsRowShown="0">
-  <autoFilter ref="A1:F2" xr:uid="{88682BFF-45CC-4F65-87CF-0204F987928D}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0EBAE740-7BC6-403C-BB9E-41DE0548C3FA}" name="AWB"/>
-    <tableColumn id="2" xr3:uid="{196AD421-FDEF-428D-8EE8-30DD6C961E5B}" name="Motorista"/>
-    <tableColumn id="3" xr3:uid="{56825D65-48F8-4F47-BA85-CDAD6E8605EA}" name="Nome"/>
-    <tableColumn id="4" xr3:uid="{4E9EE87F-F806-45BF-8459-1C60C3A68CE2}" name="Telefone"/>
-    <tableColumn id="5" xr3:uid="{73F33F7D-C27B-4BB4-8498-4EBCE8531AB9}" name="Endereco"/>
-    <tableColumn id="6" xr3:uid="{660BA362-4676-4D61-B20D-EDD96B75D755}" name="Produto"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1124,141 +741,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB946E88-CA76-406C-B1E6-F13BCD3ED444}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5B3F5F-991A-4DB8-A76A-24914CB92237}">
-  <dimension ref="A2:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" s="5"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="2">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1468,7 +950,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_23F921ED95A3C821146008C6AD0DD1CC5826805A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D658B33-01BA-437E-BE34-1D5A79754D36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="173">
   <si>
     <t>AWB</t>
   </si>
@@ -45,335 +34,513 @@
     <t>Produto</t>
   </si>
   <si>
-    <t>3320071350136</t>
+    <t>3320058338594</t>
+  </si>
+  <si>
+    <t>3320000361133</t>
+  </si>
+  <si>
+    <t>3320032360033</t>
+  </si>
+  <si>
+    <t>3320090345591</t>
+  </si>
+  <si>
+    <t>3320093352291</t>
+  </si>
+  <si>
+    <t>3320073355871</t>
+  </si>
+  <si>
+    <t>6041626233120</t>
+  </si>
+  <si>
+    <t>3320095355337</t>
+  </si>
+  <si>
+    <t>3320096343566</t>
+  </si>
+  <si>
+    <t>3320001366519</t>
+  </si>
+  <si>
+    <t>3320009365112</t>
+  </si>
+  <si>
+    <t>6041626351327</t>
+  </si>
+  <si>
+    <t>3320095352864</t>
+  </si>
+  <si>
+    <t>3320067346239</t>
+  </si>
+  <si>
+    <t>3320030367161</t>
+  </si>
+  <si>
+    <t>3320034350251</t>
+  </si>
+  <si>
+    <t>3320022366102</t>
+  </si>
+  <si>
+    <t>3320095349691</t>
+  </si>
+  <si>
+    <t>6041826674013</t>
   </si>
   <si>
     <t>3320041357597</t>
   </si>
   <si>
-    <t>3320001366519</t>
-  </si>
-  <si>
-    <t>3320058358093</t>
-  </si>
-  <si>
-    <t>3320067346239</t>
+    <t>6041726374040</t>
+  </si>
+  <si>
+    <t>3320032351125</t>
+  </si>
+  <si>
+    <t>3320053356504</t>
+  </si>
+  <si>
+    <t>3320071356438</t>
+  </si>
+  <si>
+    <t>3320065314168</t>
+  </si>
+  <si>
+    <t>6041626861261</t>
+  </si>
+  <si>
+    <t>6041426892552</t>
+  </si>
+  <si>
+    <t>3320052345018</t>
   </si>
   <si>
     <t>3320090359776</t>
   </si>
   <si>
-    <t>3320022360871</t>
-  </si>
-  <si>
-    <t>3320065314168</t>
-  </si>
-  <si>
-    <t>3320096343566</t>
-  </si>
-  <si>
-    <t>3320009365112</t>
-  </si>
-  <si>
-    <t>6041726522534</t>
-  </si>
-  <si>
-    <t>3320019348079</t>
-  </si>
-  <si>
-    <t>3320022349122</t>
-  </si>
-  <si>
-    <t>3320095349691</t>
-  </si>
-  <si>
-    <t>6041726374040</t>
-  </si>
-  <si>
-    <t>3320073355871</t>
-  </si>
-  <si>
-    <t>3320090345591</t>
-  </si>
-  <si>
-    <t>3320057350290</t>
-  </si>
-  <si>
-    <t>(JML INT)GETER HENRIQUE - ITABIRA</t>
+    <t>3320087368166</t>
+  </si>
+  <si>
+    <t>(JML INT)WINDISON MAICON - ITABIRA</t>
+  </si>
+  <si>
+    <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
+  </si>
+  <si>
+    <t>(STB LOC) CARLOS VINICIOS EFIRMIANDO</t>
+  </si>
+  <si>
+    <t>(STB LOC)DIOVANI WALISON DE ANDRADE</t>
+  </si>
+  <si>
+    <t>(STB LOC) ALINE CRISTINA SANTOS</t>
+  </si>
+  <si>
+    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
+  </si>
+  <si>
+    <t>(JML LOC) ROGER CARLOS BRAGA</t>
+  </si>
+  <si>
+    <t>(STB LOC)JOÃO HILBERT DA SILVA</t>
+  </si>
+  <si>
+    <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
+  </si>
+  <si>
+    <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
+  </si>
+  <si>
+    <t>(JML LOC) MARC RODRIGO DA COSTA SILVA</t>
   </si>
   <si>
     <t>(STB LOC) PAMELA LANA REZENDE</t>
   </si>
   <si>
-    <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
-  </si>
-  <si>
-    <t>(JML INT)WINDISON MAICON - ITABIRA</t>
-  </si>
-  <si>
-    <t>(STB LOC)JOÃO HILBERT DA SILVA</t>
+    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+  </si>
+  <si>
+    <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
+  </si>
+  <si>
+    <t>(JML INT)WHEMES LEMOS - SÃO GONÇALO</t>
   </si>
   <si>
     <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
   </si>
   <si>
-    <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
-  </si>
-  <si>
-    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
-  </si>
-  <si>
-    <t>(JML LOC) ROGER CARLOS BRAGA</t>
-  </si>
-  <si>
-    <t>(STB LOC) ALINE CRISTINA SANTOS</t>
-  </si>
-  <si>
-    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
-  </si>
-  <si>
-    <t>(STB LOC) CARLOS VINICIOS EFIRMIANDO</t>
-  </si>
-  <si>
-    <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
-  </si>
-  <si>
-    <t>(STB LOC)DIOVANI WALISON DE ANDRADE</t>
-  </si>
-  <si>
-    <t>(JML INT) LUCAS SANTOS - ITABIRA</t>
-  </si>
-  <si>
-    <t>Giseli costa Espindola Gomes</t>
+    <t>(STB LOC)MARCOS AURELIO BRAGA JUNIOR</t>
+  </si>
+  <si>
+    <t>greiciane Cristina da Costa</t>
+  </si>
+  <si>
+    <t>liza mãe João Miguel</t>
+  </si>
+  <si>
+    <t>giguerra66</t>
+  </si>
+  <si>
+    <t>Rafaela Meireles Coutinho</t>
+  </si>
+  <si>
+    <t>Adrielle Gonçalves</t>
+  </si>
+  <si>
+    <t>Joice Mara do Carmo pinto marques</t>
+  </si>
+  <si>
+    <t>Junior Lacerda</t>
+  </si>
+  <si>
+    <t>Jerusa Ariane</t>
+  </si>
+  <si>
+    <t>Kennedy Wander</t>
+  </si>
+  <si>
+    <t>Lorena Silva</t>
+  </si>
+  <si>
+    <t>Alexandra Santos</t>
+  </si>
+  <si>
+    <t>Dayane Andrade</t>
+  </si>
+  <si>
+    <t>Simone ferreira</t>
+  </si>
+  <si>
+    <t>Mariana Silva</t>
+  </si>
+  <si>
+    <t>Iago Malfitano</t>
+  </si>
+  <si>
+    <t>Jéssica Sabrina</t>
+  </si>
+  <si>
+    <t>Marielle Porfirio dos Santos</t>
+  </si>
+  <si>
+    <t>Lali</t>
+  </si>
+  <si>
+    <t>Juçara Martins de Paula</t>
   </si>
   <si>
     <t>Jenifer Kelly</t>
   </si>
   <si>
-    <t>Lorena Silva</t>
-  </si>
-  <si>
-    <t>Ruth Vitoria</t>
-  </si>
-  <si>
-    <t>Mariana Silva</t>
+    <t>Sara Cristina da Silva de Oliveira</t>
+  </si>
+  <si>
+    <t>Samanta Martins Penteados</t>
+  </si>
+  <si>
+    <t>Luciana Paiva</t>
+  </si>
+  <si>
+    <t>Thalita Nayara</t>
+  </si>
+  <si>
+    <t>daniloluz20</t>
+  </si>
+  <si>
+    <t>Marina Soares Assunção</t>
+  </si>
+  <si>
+    <t>Soleane Ferreira Quites</t>
+  </si>
+  <si>
+    <t>ray ray</t>
   </si>
   <si>
     <t>eneluciafreitas</t>
   </si>
   <si>
-    <t>diogo</t>
-  </si>
-  <si>
-    <t>daniloluz20</t>
-  </si>
-  <si>
-    <t>Kennedy Wander</t>
-  </si>
-  <si>
-    <t>Alexandra Santos</t>
-  </si>
-  <si>
-    <t>Emily Cristina da Silva Zanella</t>
-  </si>
-  <si>
-    <t>milinha Vasconcellos</t>
-  </si>
-  <si>
-    <t>Lari Lari</t>
-  </si>
-  <si>
-    <t>Lali</t>
-  </si>
-  <si>
-    <t>Sara Cristina da Silva de Oliveira</t>
-  </si>
-  <si>
-    <t>Joice Mara do Carmo pinto marques</t>
-  </si>
-  <si>
-    <t>Rafaela Meireles Coutinho</t>
-  </si>
-  <si>
-    <t>Jane kelly</t>
-  </si>
-  <si>
-    <t>+5531999368116</t>
+    <t>Cleonice Gomes</t>
+  </si>
+  <si>
+    <t>+5531957369928</t>
+  </si>
+  <si>
+    <t>+5531995035827</t>
+  </si>
+  <si>
+    <t>+5531996731204</t>
+  </si>
+  <si>
+    <t>+5531994061028</t>
+  </si>
+  <si>
+    <t>+5557197062753</t>
+  </si>
+  <si>
+    <t>+5531996862635</t>
+  </si>
+  <si>
+    <t>+5531971732198</t>
+  </si>
+  <si>
+    <t>+5531985124720</t>
+  </si>
+  <si>
+    <t>+5553191738884</t>
+  </si>
+  <si>
+    <t>+5531986090083</t>
+  </si>
+  <si>
+    <t>+5535998721133</t>
+  </si>
+  <si>
+    <t>+5531994997850</t>
+  </si>
+  <si>
+    <t>+5531997201827</t>
+  </si>
+  <si>
+    <t>+5531995050247</t>
+  </si>
+  <si>
+    <t>+5531985141983</t>
+  </si>
+  <si>
+    <t>+5531998024204</t>
+  </si>
+  <si>
+    <t>+5531981206568</t>
+  </si>
+  <si>
+    <t>+5531983648807</t>
+  </si>
+  <si>
+    <t>+5531997036776</t>
   </si>
   <si>
     <t>+5531995264171</t>
   </si>
   <si>
-    <t>+5531986090083</t>
-  </si>
-  <si>
-    <t>+5531987510691</t>
-  </si>
-  <si>
-    <t>+5531995050247</t>
+    <t>+5531995529037</t>
+  </si>
+  <si>
+    <t>+5531988399779</t>
+  </si>
+  <si>
+    <t>+5531982279477</t>
+  </si>
+  <si>
+    <t>+5531988455042</t>
+  </si>
+  <si>
+    <t>+5592982080755</t>
+  </si>
+  <si>
+    <t>+5531996590550</t>
+  </si>
+  <si>
+    <t>+5531996661097</t>
+  </si>
+  <si>
+    <t>+5531991575566</t>
   </si>
   <si>
     <t>+5531998675818</t>
   </si>
   <si>
-    <t>+5527981191289</t>
-  </si>
-  <si>
-    <t>+5592982080755</t>
-  </si>
-  <si>
-    <t>+5553191738884</t>
-  </si>
-  <si>
-    <t>+5535998721133</t>
-  </si>
-  <si>
-    <t>+5531982629023</t>
-  </si>
-  <si>
-    <t>+5531982151895</t>
-  </si>
-  <si>
-    <t>+5531994361780</t>
-  </si>
-  <si>
-    <t>+5531983648807</t>
-  </si>
-  <si>
-    <t>+5531995529037</t>
-  </si>
-  <si>
-    <t>+5531996862635</t>
-  </si>
-  <si>
-    <t>+5531994061028</t>
-  </si>
-  <si>
-    <t>+5531990708633</t>
-  </si>
-  <si>
-    <t>Rua Ipê Roxo 147 casa, Jardim dos Ipês, Itabira</t>
+    <t>+5531996688180</t>
+  </si>
+  <si>
+    <t>Rua São Pedro 530, Santa Marta, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Nélson Figueiredo 86 casa fundos portão vermelho, Eldorado, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Água Santa 90, centro, Itabira</t>
+  </si>
+  <si>
+    <t>Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara</t>
+  </si>
+  <si>
+    <t>Rua Três 207 casa, Barreiro, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Olegário Maciel 69 casa, Lagoa, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>R. Joaquim Rufino do 180 Rua do posto de, Garcia, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Rua Fagundes Varela 79, João XXIII, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
+  </si>
+  <si>
+    <t>Avenida Machado de Assis 29A, Machado, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Matilde Brangaça Pereira 40 casa, Fênix, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Padre Teles 533 Casa Fundos, Vila São Geraldo, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Avenida Rui Barbosa 52 Casa, Machado, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Pintassilgo 144, Pedreira, Itabira</t>
+  </si>
+  <si>
+    <t>Avenida Gentil Bicalho 991 Sala 103, Carneirinhos, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Osvaldo Bastos Werneck 207 Casa, Centro, Sem-Peixe</t>
+  </si>
+  <si>
+    <t>Rua Monte Castelo Próximo à igreja Batista, Belmonte, João Monlevade</t>
   </si>
   <si>
     <t>rua Francis Hime 397 casa do fundo, Irmãos Aleme, Barão de Cocais</t>
   </si>
   <si>
-    <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Afonso Arinos 33 casa, João XXIII, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Padre Teles 533 Casa Fundos, Vila São Geraldo, Barão de Cocais</t>
+    <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Amor-Perfeito 46 Casa, São Pedro, Itabira</t>
+  </si>
+  <si>
+    <t>Praça São Sebastião 220 Casa, Centro, Sem-Peixe</t>
+  </si>
+  <si>
+    <t>Rua Nélson Figueiredo 98, Eldorado, Itabira</t>
+  </si>
+  <si>
+    <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Fernando Dias de Carvalho 305, Centro, Ferros</t>
+  </si>
+  <si>
+    <t>Sitio faxina Casa, Faxina, São Gonçalo do Rio Abaixo</t>
+  </si>
+  <si>
+    <t>Rua joão pinheiro 117 Loja, Sorveteria, Centro, Itabira</t>
   </si>
   <si>
     <t>Rua Colatina 393, Industrial, João Monlevade</t>
   </si>
   <si>
-    <t>Rua Caetés 145 Casa, Industrial, João Monlevade</t>
-  </si>
-  <si>
-    <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
-  </si>
-  <si>
-    <t>rua izolina raimunda a silva, 145 -, garcia, Barão de Cocais</t>
-  </si>
-  <si>
-    <t>Rua Joaquim Gomes Bastos 51, Laranjeiras, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Pitangui s/n Casa com cerca, próximo ao bar, Ponte coronel, São Gonçalo do Rio Abaixo</t>
-  </si>
-  <si>
-    <t>Rua Osvaldo Bastos Werneck 207 Casa, Centro, Sem-Peixe</t>
-  </si>
-  <si>
-    <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Olegário Maciel 69 casa, Lagoa, Barão de Cocais</t>
-  </si>
-  <si>
-    <t>Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara</t>
-  </si>
-  <si>
-    <t>Rua Benedito Valadares 10 A, Doze de Março, Itabira</t>
-  </si>
-  <si>
-    <t>Casaco Teddy Plus Size Feminino Longo Pelinho Com Capuz*1</t>
+    <t>Terminal rodoviário São João do morro grande 1 Rodoviária, Avenida Wilson Alvarenga 190, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Body Splash Desodorante Colônia 200ml Inspiração Alta Fixação - Sly Cosméticos*1</t>
+  </si>
+  <si>
+    <t>Kit 3 Calças Infantil Chimpa Flanelado Inverno 2 ao 16*1</t>
+  </si>
+  <si>
+    <t>Bolsa Feminina Transversal Bolsa de Mão Casamento Clutch Alça Removivel Lançamento*1</t>
+  </si>
+  <si>
+    <t>Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1</t>
+  </si>
+  <si>
+    <t>Carregador Portátil Pineng Power Bank 10.000mah,5000mah com adaptador iPhone,V8*1</t>
+  </si>
+  <si>
+    <t>Conjunto Feminino Inverno Plush. Tamanhos: P ao Plus Size - Com zíper, capuz e bolso. Agasalho quentinho, liso e básico moda curve*1</t>
+  </si>
+  <si>
+    <t>DIVERSOS*1</t>
+  </si>
+  <si>
+    <t>Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*2+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1</t>
+  </si>
+  <si>
+    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
+  </si>
+  <si>
+    <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
+  </si>
+  <si>
+    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
+  </si>
+  <si>
+    <t>Colete de tecido feminino*1</t>
+  </si>
+  <si>
+    <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
+  </si>
+  <si>
+    <t>Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1+Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1</t>
+  </si>
+  <si>
+    <t>Maquina Cortar Cabelo KM Profissional Grafites Max-2092 Cor Estampada*1</t>
+  </si>
+  <si>
+    <t>Body Feminino Renda Manga Longa Tendência*1</t>
+  </si>
+  <si>
+    <t>Meia 3D Divertida Infantil Cano Alto Com Desenho Animado–Meias até o joelho com estampa 3D | Alta qualidade, presente perfeito para meninas/mininos,Tamanho Único Veste 32 ao 38*1</t>
+  </si>
+  <si>
+    <t>Colar semi joia arvore da vida corrente veneziana verniz italiano*1</t>
+  </si>
+  <si>
+    <t>Conjunto de pijama menino*1+Vestuário Masculino Infantil*1+Vestuário Masculino Infantil*1</t>
   </si>
   <si>
     <t>Escova de Limpeza Esfregão 3 Em 1 vassoura rodo chão cozinha Banheiro*1</t>
   </si>
   <si>
-    <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
-  </si>
-  <si>
-    <t>Projetor HY300 Portátil Smart Android 11 4K Ultra HD Wifi Bluetooth Cinema em Casa com Alto Falante*1</t>
-  </si>
-  <si>
-    <t>Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1+Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1</t>
+    <t>Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1</t>
+  </si>
+  <si>
+    <t>Calça Jeans MOM Feminina Cintura Alta Qualidade Premiun*1</t>
+  </si>
+  <si>
+    <t>Casaco Fitness Feminino com Zíper E Bolsa que Valoriza o Corpo | Look Academia Elegante*1+Casaco Fitness Feminino com Zíper E Bolsa que Valoriza o Corpo | Look Academia Elegante*1</t>
+  </si>
+  <si>
+    <t>Body Renda Floral Manga Longa Tule Transparente Moda Feminina Inverno Sexy*1</t>
+  </si>
+  <si>
+    <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
+  </si>
+  <si>
+    <t>Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1</t>
+  </si>
+  <si>
+    <t>Terno masculino*1</t>
+  </si>
+  <si>
+    <t>KIT 3 Calça Jeans Feminina Wide Leg pantalona Cintura Alta Oferta especial entrega em 24 horas Outlet de fábrica*1</t>
   </si>
   <si>
     <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
   </si>
   <si>
-    <t>Boné de Beisebol Estilo Vintage Jeans Lavado Ajustável Unissex Várias Cores e Modelos Proteção Solar bonetistore mia snapback chapéu*1</t>
-  </si>
-  <si>
-    <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
-  </si>
-  <si>
-    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
-  </si>
-  <si>
-    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
-  </si>
-  <si>
-    <t>DIVERSOS*1</t>
-  </si>
-  <si>
-    <t>Super Macio Peruca Cacheada Repartida ao Meio Fibra Orgânica Peruca Encaracolado Africano Wig Premium MILA + Gratis Wig Cap*1</t>
-  </si>
-  <si>
-    <t>Depilador elétrico com navalha dupla cuidado e delicadeza com sua pele, Recarregável com Tecnologia avançada Indolor.*1</t>
-  </si>
-  <si>
-    <t>Colar semi joia arvore da vida corrente veneziana verniz italiano*1</t>
-  </si>
-  <si>
-    <t>Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1</t>
-  </si>
-  <si>
-    <t>Conjunto Feminino Inverno Plush. Tamanhos: P ao Plus Size - Com zíper, capuz e bolso. Agasalho quentinho, liso e básico moda curve*1</t>
-  </si>
-  <si>
-    <t>Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1</t>
-  </si>
-  <si>
-    <t>Kit 11 Frascos Porta Shampoo/ Cremes/ Plastico Para Viagem -S1*1</t>
+    <t>Porta Organizador De Mesa Coelhos Fofo Gaveta Treco Maquiagem De Mesa Pequeno Multifuncional Estilo Minimalista*1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -401,28 +568,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -464,7 +622,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -496,27 +654,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -548,24 +688,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -741,15 +863,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -769,307 +887,307 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1077,56 +1195,296 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="F17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="F18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
         <v>74</v>
       </c>
-      <c r="E19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="D23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F28" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" t="s">
         <v>110</v>
+      </c>
+      <c r="E29" t="s">
+        <v>140</v>
+      </c>
+      <c r="F29" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_23F921EDABF3C91DEE6008C675CE607B4A228F2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF0D805-F8C6-46B8-9024-3B8B196DA0AB}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="155">
   <si>
     <t>AWB</t>
   </si>
@@ -43,9 +54,6 @@
     <t>3320032360033</t>
   </si>
   <si>
-    <t>3320090345591</t>
-  </si>
-  <si>
     <t>3320093352291</t>
   </si>
   <si>
@@ -64,9 +72,6 @@
     <t>3320001366519</t>
   </si>
   <si>
-    <t>3320009365112</t>
-  </si>
-  <si>
     <t>6041626351327</t>
   </si>
   <si>
@@ -91,9 +96,6 @@
     <t>6041826674013</t>
   </si>
   <si>
-    <t>3320041357597</t>
-  </si>
-  <si>
     <t>6041726374040</t>
   </si>
   <si>
@@ -130,9 +132,6 @@
     <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
   </si>
   <si>
-    <t>(STB LOC) CARLOS VINICIOS EFIRMIANDO</t>
-  </si>
-  <si>
     <t>(STB LOC)DIOVANI WALISON DE ANDRADE</t>
   </si>
   <si>
@@ -142,9 +141,6 @@
     <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
   </si>
   <si>
-    <t>(JML LOC) ROGER CARLOS BRAGA</t>
-  </si>
-  <si>
     <t>(STB LOC)JOÃO HILBERT DA SILVA</t>
   </si>
   <si>
@@ -157,9 +153,6 @@
     <t>(JML LOC) MARC RODRIGO DA COSTA SILVA</t>
   </si>
   <si>
-    <t>(STB LOC) PAMELA LANA REZENDE</t>
-  </si>
-  <si>
     <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
   </si>
   <si>
@@ -184,9 +177,6 @@
     <t>giguerra66</t>
   </si>
   <si>
-    <t>Rafaela Meireles Coutinho</t>
-  </si>
-  <si>
     <t>Adrielle Gonçalves</t>
   </si>
   <si>
@@ -205,9 +195,6 @@
     <t>Lorena Silva</t>
   </si>
   <si>
-    <t>Alexandra Santos</t>
-  </si>
-  <si>
     <t>Dayane Andrade</t>
   </si>
   <si>
@@ -232,9 +219,6 @@
     <t>Juçara Martins de Paula</t>
   </si>
   <si>
-    <t>Jenifer Kelly</t>
-  </si>
-  <si>
     <t>Sara Cristina da Silva de Oliveira</t>
   </si>
   <si>
@@ -274,9 +258,6 @@
     <t>+5531996731204</t>
   </si>
   <si>
-    <t>+5531994061028</t>
-  </si>
-  <si>
     <t>+5557197062753</t>
   </si>
   <si>
@@ -295,9 +276,6 @@
     <t>+5531986090083</t>
   </si>
   <si>
-    <t>+5535998721133</t>
-  </si>
-  <si>
     <t>+5531994997850</t>
   </si>
   <si>
@@ -322,9 +300,6 @@
     <t>+5531997036776</t>
   </si>
   <si>
-    <t>+5531995264171</t>
-  </si>
-  <si>
     <t>+5531995529037</t>
   </si>
   <si>
@@ -364,9 +339,6 @@
     <t>Rua Água Santa 90, centro, Itabira</t>
   </si>
   <si>
-    <t>Av. Conselheiro Afonso Pena 475 Loja na esquina, Centro, Santa Bárbara</t>
-  </si>
-  <si>
     <t>Rua Três 207 casa, Barreiro, Itabira</t>
   </si>
   <si>
@@ -385,9 +357,6 @@
     <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
   </si>
   <si>
-    <t>Rua Jasmim 44 Casa, Vila Tanque, João Monlevade</t>
-  </si>
-  <si>
     <t>Avenida Machado de Assis 29A, Machado, Itabira</t>
   </si>
   <si>
@@ -412,9 +381,6 @@
     <t>Rua Monte Castelo Próximo à igreja Batista, Belmonte, João Monlevade</t>
   </si>
   <si>
-    <t>rua Francis Hime 397 casa do fundo, Irmãos Aleme, Barão de Cocais</t>
-  </si>
-  <si>
     <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
   </si>
   <si>
@@ -454,9 +420,6 @@
     <t>Bolsa Feminina Transversal Bolsa de Mão Casamento Clutch Alça Removivel Lançamento*1</t>
   </si>
   <si>
-    <t>Capa De Telefone Com Ventosa 3D Para iPhone 17 16 15 14 13 12 11 Pro Max X XS XR À Prova De Choque*1</t>
-  </si>
-  <si>
     <t>Carregador Portátil Pineng Power Bank 10.000mah,5000mah com adaptador iPhone,V8*1</t>
   </si>
   <si>
@@ -475,9 +438,6 @@
     <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
   </si>
   <si>
-    <t>Jogo Memória Eletrônico Infantil Quatro Cores Genius Sons e Luzes ENVIO RÁPIDO*1</t>
-  </si>
-  <si>
     <t>Colete de tecido feminino*1</t>
   </si>
   <si>
@@ -500,9 +460,6 @@
   </si>
   <si>
     <t>Conjunto de pijama menino*1+Vestuário Masculino Infantil*1+Vestuário Masculino Infantil*1</t>
-  </si>
-  <si>
-    <t>Escova de Limpeza Esfregão 3 Em 1 vassoura rodo chão cozinha Banheiro*1</t>
   </si>
   <si>
     <t>Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1</t>
@@ -538,8 +495,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -576,11 +533,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -622,7 +587,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -654,9 +619,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -688,6 +671,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -863,11 +864,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -887,604 +891,544 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F19" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F21" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F22" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F27" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" t="s">
-        <v>140</v>
-      </c>
-      <c r="F29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>141</v>
-      </c>
-      <c r="F30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" t="s">
-        <v>142</v>
-      </c>
-      <c r="F31" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_23F921EDABF3C91DEE6008C675CE607B4A228F2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF0D805-F8C6-46B8-9024-3B8B196DA0AB}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_23F921EDABF3C91DEE6008C675CE607B4A228F2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B5D8D4E-A356-4818-972C-9E845E54E65A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
   <si>
     <t>AWB</t>
   </si>
@@ -57,24 +57,9 @@
     <t>3320093352291</t>
   </si>
   <si>
-    <t>3320073355871</t>
-  </si>
-  <si>
-    <t>6041626233120</t>
-  </si>
-  <si>
-    <t>3320095355337</t>
-  </si>
-  <si>
-    <t>3320096343566</t>
-  </si>
-  <si>
     <t>3320001366519</t>
   </si>
   <si>
-    <t>6041626351327</t>
-  </si>
-  <si>
     <t>3320095352864</t>
   </si>
   <si>
@@ -102,9 +87,6 @@
     <t>3320032351125</t>
   </si>
   <si>
-    <t>3320053356504</t>
-  </si>
-  <si>
     <t>3320071356438</t>
   </si>
   <si>
@@ -132,15 +114,6 @@
     <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
   </si>
   <si>
-    <t>(STB LOC)DIOVANI WALISON DE ANDRADE</t>
-  </si>
-  <si>
-    <t>(STB LOC) ALINE CRISTINA SANTOS</t>
-  </si>
-  <si>
-    <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
-  </si>
-  <si>
     <t>(STB LOC)JOÃO HILBERT DA SILVA</t>
   </si>
   <si>
@@ -180,24 +153,9 @@
     <t>Adrielle Gonçalves</t>
   </si>
   <si>
-    <t>Joice Mara do Carmo pinto marques</t>
-  </si>
-  <si>
-    <t>Junior Lacerda</t>
-  </si>
-  <si>
-    <t>Jerusa Ariane</t>
-  </si>
-  <si>
-    <t>Kennedy Wander</t>
-  </si>
-  <si>
     <t>Lorena Silva</t>
   </si>
   <si>
-    <t>Dayane Andrade</t>
-  </si>
-  <si>
     <t>Simone ferreira</t>
   </si>
   <si>
@@ -225,9 +183,6 @@
     <t>Samanta Martins Penteados</t>
   </si>
   <si>
-    <t>Luciana Paiva</t>
-  </si>
-  <si>
     <t>Thalita Nayara</t>
   </si>
   <si>
@@ -261,24 +216,9 @@
     <t>+5557197062753</t>
   </si>
   <si>
-    <t>+5531996862635</t>
-  </si>
-  <si>
-    <t>+5531971732198</t>
-  </si>
-  <si>
-    <t>+5531985124720</t>
-  </si>
-  <si>
-    <t>+5553191738884</t>
-  </si>
-  <si>
     <t>+5531986090083</t>
   </si>
   <si>
-    <t>+5531994997850</t>
-  </si>
-  <si>
     <t>+5531997201827</t>
   </si>
   <si>
@@ -306,9 +246,6 @@
     <t>+5531988399779</t>
   </si>
   <si>
-    <t>+5531982279477</t>
-  </si>
-  <si>
     <t>+5531988455042</t>
   </si>
   <si>
@@ -342,24 +279,9 @@
     <t>Rua Três 207 casa, Barreiro, Itabira</t>
   </si>
   <si>
-    <t>Rua Olegário Maciel 69 casa, Lagoa, Barão de Cocais</t>
-  </si>
-  <si>
-    <t>R. Joaquim Rufino do 180 Rua do posto de, Garcia, Barão de Cocais</t>
-  </si>
-  <si>
-    <t>Rua Fagundes Varela 79, João XXIII, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Jesus Drumond 110 Apartamento B, Nova Monlevade, João Monlevade</t>
-  </si>
-  <si>
     <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
   </si>
   <si>
-    <t>Avenida Machado de Assis 29A, Machado, Itabira</t>
-  </si>
-  <si>
     <t>Rua Matilde Brangaça Pereira 40 casa, Fênix, Itabira</t>
   </si>
   <si>
@@ -387,9 +309,6 @@
     <t>Rua Amor-Perfeito 46 Casa, São Pedro, Itabira</t>
   </si>
   <si>
-    <t>Praça São Sebastião 220 Casa, Centro, Sem-Peixe</t>
-  </si>
-  <si>
     <t>Rua Nélson Figueiredo 98, Eldorado, Itabira</t>
   </si>
   <si>
@@ -423,24 +342,9 @@
     <t>Carregador Portátil Pineng Power Bank 10.000mah,5000mah com adaptador iPhone,V8*1</t>
   </si>
   <si>
-    <t>Conjunto Feminino Inverno Plush. Tamanhos: P ao Plus Size - Com zíper, capuz e bolso. Agasalho quentinho, liso e básico moda curve*1</t>
-  </si>
-  <si>
-    <t>DIVERSOS*1</t>
-  </si>
-  <si>
-    <t>Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*2+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1+Óculos de sol Tamanhos masculinos e femininos, diversas cores e estilos, proteção UV400 Liquidação*1</t>
-  </si>
-  <si>
-    <t>Guarda-Chuva Grande Automático - Fibra de Vidro Blackout para Proteção UV, Reforçado para Tempestade*1</t>
-  </si>
-  <si>
     <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
   </si>
   <si>
-    <t>Colete de tecido feminino*1</t>
-  </si>
-  <si>
     <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
   </si>
   <si>
@@ -466,9 +370,6 @@
   </si>
   <si>
     <t>Calça Jeans MOM Feminina Cintura Alta Qualidade Premiun*1</t>
-  </si>
-  <si>
-    <t>Casaco Fitness Feminino com Zíper E Bolsa que Valoriza o Corpo | Look Academia Elegante*1+Casaco Fitness Feminino com Zíper E Bolsa que Valoriza o Corpo | Look Academia Elegante*1</t>
   </si>
   <si>
     <t>Body Renda Floral Manga Longa Tule Transparente Moda Feminina Inverno Sexy*1</t>
@@ -865,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -896,19 +797,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" t="s">
         <v>101</v>
-      </c>
-      <c r="F2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -916,19 +817,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
         <v>102</v>
-      </c>
-      <c r="F3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,19 +837,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" t="s">
         <v>103</v>
-      </c>
-      <c r="F4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -956,19 +857,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" t="s">
         <v>104</v>
-      </c>
-      <c r="F5" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -976,19 +877,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s">
         <v>105</v>
-      </c>
-      <c r="F6" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -996,19 +897,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
         <v>106</v>
-      </c>
-      <c r="F7" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1016,19 +917,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" t="s">
         <v>107</v>
-      </c>
-      <c r="F8" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1036,19 +937,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
         <v>108</v>
-      </c>
-      <c r="F9" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1056,19 +957,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" t="s">
         <v>109</v>
-      </c>
-      <c r="F10" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1076,19 +977,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" t="s">
         <v>110</v>
-      </c>
-      <c r="F11" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,19 +997,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" t="s">
         <v>111</v>
-      </c>
-      <c r="F12" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,19 +1017,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" t="s">
         <v>112</v>
-      </c>
-      <c r="F13" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1139,16 +1040,16 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" t="s">
         <v>113</v>
-      </c>
-      <c r="F14" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1156,19 +1057,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" t="s">
         <v>114</v>
-      </c>
-      <c r="F15" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1176,19 +1077,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" t="s">
         <v>115</v>
-      </c>
-      <c r="F16" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1196,19 +1097,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" t="s">
         <v>116</v>
-      </c>
-      <c r="F17" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1216,19 +1117,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" t="s">
         <v>117</v>
-      </c>
-      <c r="F18" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1236,19 +1137,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" t="s">
         <v>118</v>
-      </c>
-      <c r="F19" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1256,19 +1157,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s">
         <v>119</v>
-      </c>
-      <c r="F20" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1276,19 +1177,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" t="s">
         <v>120</v>
-      </c>
-      <c r="F21" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1296,142 +1197,23 @@
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" t="s">
         <v>121</v>
-      </c>
-      <c r="F22" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" t="s">
-        <v>123</v>
-      </c>
-      <c r="F24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" t="s">
-        <v>125</v>
-      </c>
-      <c r="F26" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" t="s">
-        <v>126</v>
-      </c>
-      <c r="F27" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_23F921EDABF3C91DEE6008C675CE607B4A228F2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B5D8D4E-A356-4818-972C-9E845E54E65A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="144">
   <si>
     <t>AWB</t>
   </si>
@@ -45,100 +34,151 @@
     <t>Produto</t>
   </si>
   <si>
+    <t>3320093352291</t>
+  </si>
+  <si>
+    <t>3320090348959</t>
+  </si>
+  <si>
+    <t>3320095352864</t>
+  </si>
+  <si>
+    <t>3320087368166</t>
+  </si>
+  <si>
+    <t>6041626126467</t>
+  </si>
+  <si>
+    <t>6041726374040</t>
+  </si>
+  <si>
+    <t>3320095349691</t>
+  </si>
+  <si>
+    <t>6041626588141</t>
+  </si>
+  <si>
+    <t>6041826674013</t>
+  </si>
+  <si>
+    <t>3320081358713</t>
+  </si>
+  <si>
+    <t>3320064342322</t>
+  </si>
+  <si>
     <t>3320058338594</t>
   </si>
   <si>
+    <t>3320034361855</t>
+  </si>
+  <si>
+    <t>6040226346133</t>
+  </si>
+  <si>
+    <t>6041726248902</t>
+  </si>
+  <si>
+    <t>3320032351125</t>
+  </si>
+  <si>
+    <t>3320065314168</t>
+  </si>
+  <si>
+    <t>6041626242474</t>
+  </si>
+  <si>
+    <t>3320032360033</t>
+  </si>
+  <si>
     <t>3320000361133</t>
   </si>
   <si>
-    <t>3320032360033</t>
-  </si>
-  <si>
-    <t>3320093352291</t>
-  </si>
-  <si>
-    <t>3320001366519</t>
-  </si>
-  <si>
-    <t>3320095352864</t>
-  </si>
-  <si>
-    <t>3320067346239</t>
-  </si>
-  <si>
-    <t>3320030367161</t>
-  </si>
-  <si>
-    <t>3320034350251</t>
-  </si>
-  <si>
-    <t>3320022366102</t>
-  </si>
-  <si>
-    <t>3320095349691</t>
-  </si>
-  <si>
-    <t>6041826674013</t>
-  </si>
-  <si>
-    <t>6041726374040</t>
-  </si>
-  <si>
-    <t>3320032351125</t>
-  </si>
-  <si>
-    <t>3320071356438</t>
-  </si>
-  <si>
-    <t>3320065314168</t>
+    <t>3320097342524</t>
+  </si>
+  <si>
+    <t>6041426892552</t>
+  </si>
+  <si>
+    <t>3320024360562</t>
+  </si>
+  <si>
+    <t>3320098367249</t>
   </si>
   <si>
     <t>6041626861261</t>
   </si>
   <si>
-    <t>6041426892552</t>
-  </si>
-  <si>
-    <t>3320052345018</t>
-  </si>
-  <si>
     <t>3320090359776</t>
   </si>
   <si>
-    <t>3320087368166</t>
-  </si>
-  <si>
     <t>(JML INT)WINDISON MAICON - ITABIRA</t>
   </si>
   <si>
     <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
   </si>
   <si>
-    <t>(STB LOC)JOÃO HILBERT DA SILVA</t>
+    <t>(STB LOC)MARCOS AURELIO BRAGA JUNIOR</t>
+  </si>
+  <si>
+    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+  </si>
+  <si>
+    <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
+  </si>
+  <si>
+    <t>(JML LOC) MARC RODRIGO DA COSTA SILVA</t>
+  </si>
+  <si>
+    <t>(JML INT) LUCAS SANTOS - ITABIRA</t>
   </si>
   <si>
     <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
   </si>
   <si>
-    <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
-  </si>
-  <si>
-    <t>(JML LOC) MARC RODRIGO DA COSTA SILVA</t>
-  </si>
-  <si>
-    <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+    <t>(JML INT)WHEMES LEMOS - SÃO GONÇALO</t>
+  </si>
+  <si>
+    <t>(JML LOC) LUCAS DE SOUZA SILVA</t>
   </si>
   <si>
     <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
   </si>
   <si>
-    <t>(JML INT)WHEMES LEMOS - SÃO GONÇALO</t>
-  </si>
-  <si>
     <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
   </si>
   <si>
-    <t>(STB LOC)MARCOS AURELIO BRAGA JUNIOR</t>
+    <t>Adrielle Gonçalves</t>
+  </si>
+  <si>
+    <t>danielmiranda1540</t>
+  </si>
+  <si>
+    <t>Simone ferreira</t>
+  </si>
+  <si>
+    <t>Cleonice Gomes</t>
+  </si>
+  <si>
+    <t>Raíssa Estefany Santos Oliveira</t>
+  </si>
+  <si>
+    <t>Sara Cristina da Silva de Oliveira</t>
+  </si>
+  <si>
+    <t>Lali</t>
+  </si>
+  <si>
+    <t>Aline Oliveira Silva</t>
+  </si>
+  <si>
+    <t>Juçara Martins de Paula</t>
+  </si>
+  <si>
+    <t>Neey Barber</t>
+  </si>
+  <si>
+    <t>thalisalexandre72</t>
   </si>
   <si>
     <t>greiciane Cristina da Costa</t>
@@ -147,61 +187,70 @@
     <t>liza mãe João Miguel</t>
   </si>
   <si>
+    <t>Beatriz Azevedo Barcelos</t>
+  </si>
+  <si>
+    <t>Vanderleia dias de moura</t>
+  </si>
+  <si>
+    <t>Samanta Martins Penteados</t>
+  </si>
+  <si>
+    <t>daniloluz20</t>
+  </si>
+  <si>
+    <t>Maira Almeida</t>
+  </si>
+  <si>
     <t>giguerra66</t>
   </si>
   <si>
-    <t>Adrielle Gonçalves</t>
-  </si>
-  <si>
-    <t>Lorena Silva</t>
-  </si>
-  <si>
-    <t>Simone ferreira</t>
-  </si>
-  <si>
-    <t>Mariana Silva</t>
-  </si>
-  <si>
-    <t>Iago Malfitano</t>
-  </si>
-  <si>
-    <t>Jéssica Sabrina</t>
-  </si>
-  <si>
-    <t>Marielle Porfirio dos Santos</t>
-  </si>
-  <si>
-    <t>Lali</t>
-  </si>
-  <si>
-    <t>Juçara Martins de Paula</t>
-  </si>
-  <si>
-    <t>Sara Cristina da Silva de Oliveira</t>
-  </si>
-  <si>
-    <t>Samanta Martins Penteados</t>
-  </si>
-  <si>
-    <t>Thalita Nayara</t>
-  </si>
-  <si>
-    <t>daniloluz20</t>
+    <t>Larissa Nayra</t>
+  </si>
+  <si>
+    <t>Soleane Ferreira Quites</t>
+  </si>
+  <si>
+    <t>brunavfs</t>
+  </si>
+  <si>
+    <t>Ramieller Douglas</t>
   </si>
   <si>
     <t>Marina Soares Assunção</t>
   </si>
   <si>
-    <t>Soleane Ferreira Quites</t>
-  </si>
-  <si>
-    <t>ray ray</t>
-  </si>
-  <si>
     <t>eneluciafreitas</t>
   </si>
   <si>
-    <t>Cleonice Gomes</t>
+    <t>+5557197062753</t>
+  </si>
+  <si>
+    <t>+5531987135734</t>
+  </si>
+  <si>
+    <t>+5531997201827</t>
+  </si>
+  <si>
+    <t>+5531996688180</t>
+  </si>
+  <si>
+    <t>+5531995529037</t>
+  </si>
+  <si>
+    <t>+5531983648807</t>
+  </si>
+  <si>
+    <t>+5531986384873</t>
+  </si>
+  <si>
+    <t>+5531997036776</t>
+  </si>
+  <si>
+    <t>+5531971031527</t>
+  </si>
+  <si>
+    <t>+5531971181590</t>
   </si>
   <si>
     <t>+5531957369928</t>
@@ -210,61 +259,73 @@
     <t>+5531995035827</t>
   </si>
   <si>
+    <t>+5531991914681</t>
+  </si>
+  <si>
+    <t>+5531999929483</t>
+  </si>
+  <si>
+    <t>+5531988399779</t>
+  </si>
+  <si>
+    <t>+5592982080755</t>
+  </si>
+  <si>
+    <t>+5531997712507</t>
+  </si>
+  <si>
     <t>+5531996731204</t>
   </si>
   <si>
-    <t>+5557197062753</t>
-  </si>
-  <si>
-    <t>+5531986090083</t>
-  </si>
-  <si>
-    <t>+5531997201827</t>
-  </si>
-  <si>
-    <t>+5531995050247</t>
-  </si>
-  <si>
-    <t>+5531985141983</t>
-  </si>
-  <si>
-    <t>+5531998024204</t>
-  </si>
-  <si>
-    <t>+5531981206568</t>
-  </si>
-  <si>
-    <t>+5531983648807</t>
-  </si>
-  <si>
-    <t>+5531997036776</t>
-  </si>
-  <si>
-    <t>+5531995529037</t>
-  </si>
-  <si>
-    <t>+5531988399779</t>
-  </si>
-  <si>
-    <t>+5531988455042</t>
-  </si>
-  <si>
-    <t>+5592982080755</t>
+    <t>+5531999928656</t>
+  </si>
+  <si>
+    <t>+5531996661097</t>
+  </si>
+  <si>
+    <t>+5531992449975</t>
+  </si>
+  <si>
+    <t>+5531975092030</t>
   </si>
   <si>
     <t>+5531996590550</t>
   </si>
   <si>
-    <t>+5531996661097</t>
-  </si>
-  <si>
-    <t>+5531991575566</t>
-  </si>
-  <si>
     <t>+5531998675818</t>
   </si>
   <si>
-    <t>+5531996688180</t>
+    <t>Rua Três 207 casa, Barreiro, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Água Santa 90 casa, Centro, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Matilde Brangaça Pereira 40 casa, Fênix, Itabira</t>
+  </si>
+  <si>
+    <t>Terminal rodoviário São João do morro grande 1 Rodoviária, Avenida Wilson Alvarenga 190, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Rua Princesa Izabel Casa - (Após Gráfica VIP virar á esquerda), Centro, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Osvaldo Bastos Werneck 207 Casa, Centro, Sem-Peixe</t>
+  </si>
+  <si>
+    <t>Rua Valdemar de Alvarenga Lage- até 716/717 Loja LG Confecções, Água Fresca, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Monte Castelo Próximo à igreja Batista, Belmonte, João Monlevade</t>
+  </si>
+  <si>
+    <t>Avenida Duque de Caxias 340 Loja 3, Quatorze de Fevereiro, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Esmeralda 14 Loja, Centro, Itabira</t>
   </si>
   <si>
     <t>Rua São Pedro 530, Santa Marta, Itabira</t>
@@ -273,131 +334,125 @@
     <t>Rua Nélson Figueiredo 86 casa fundos portão vermelho, Eldorado, Itabira</t>
   </si>
   <si>
+    <t>Avenida France de Paula Andrade- número 35a, Vila Paciência Casa, Vila Nações Unidas, Itabira</t>
+  </si>
+  <si>
+    <t>Centro Hotel, Rua sao jose centro, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Amor-Perfeito 46 Casa, São Pedro, Itabira</t>
+  </si>
+  <si>
+    <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Raul Pompéia, João XXIII, Itabira</t>
+  </si>
+  <si>
     <t>Rua Água Santa 90, centro, Itabira</t>
   </si>
   <si>
-    <t>Rua Três 207 casa, Barreiro, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Maurílio Martins de Souza 43, Fênix, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Matilde Brangaça Pereira 40 casa, Fênix, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Padre Teles 533 Casa Fundos, Vila São Geraldo, Barão de Cocais</t>
-  </si>
-  <si>
-    <t>Avenida Rui Barbosa 52 Casa, Machado, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Pintassilgo 144, Pedreira, Itabira</t>
-  </si>
-  <si>
-    <t>Avenida Gentil Bicalho 991 Sala 103, Carneirinhos, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Osvaldo Bastos Werneck 207 Casa, Centro, Sem-Peixe</t>
-  </si>
-  <si>
-    <t>Rua Monte Castelo Próximo à igreja Batista, Belmonte, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Argentina número 61 bairro metalúrgico, Metalúrgico, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Amor-Perfeito 46 Casa, São Pedro, Itabira</t>
-  </si>
-  <si>
-    <t>Rua Nélson Figueiredo 98, Eldorado, Itabira</t>
-  </si>
-  <si>
-    <t>Avenida Getúlio Vargas 4375 Apartamento 201, Carneirinhos, João Monlevade</t>
+    <t>Avenida Osório Sampaio 832, Vila Santa Rosa, Itabira</t>
+  </si>
+  <si>
+    <t>Sitio faxina Casa, Faxina, São Gonçalo do Rio Abaixo</t>
+  </si>
+  <si>
+    <t>Rua Dona Modestina 511 loja 6, Quatorze de Fevereiro, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Industrial 400, Rosário, João Monlevade</t>
   </si>
   <si>
     <t>Rua Fernando Dias de Carvalho 305, Centro, Ferros</t>
   </si>
   <si>
-    <t>Sitio faxina Casa, Faxina, São Gonçalo do Rio Abaixo</t>
-  </si>
-  <si>
-    <t>Rua joão pinheiro 117 Loja, Sorveteria, Centro, Itabira</t>
-  </si>
-  <si>
     <t>Rua Colatina 393, Industrial, João Monlevade</t>
   </si>
   <si>
-    <t>Terminal rodoviário São João do morro grande 1 Rodoviária, Avenida Wilson Alvarenga 190, Barão de Cocais</t>
+    <t>Carregador Portátil Pineng Power Bank 10.000mah,5000mah com adaptador iPhone,V8*1</t>
+  </si>
+  <si>
+    <t>Suporte de Talheres Dourado e Prata em Aço Inox – Suporte para 24 Peças (Somente Suporte) Kit De Utensílios De Cozinha Conjuntos De Louça Modernos*1</t>
+  </si>
+  <si>
+    <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
+  </si>
+  <si>
+    <t>Porta Organizador De Mesa Coelhos Fofo Gaveta Treco Maquiagem De Mesa Pequeno Multifuncional Estilo Minimalista*1</t>
+  </si>
+  <si>
+    <t>Vestido feminino*1+Jaqueta feminina de tecido*1+Colete de tecido feminino*1+Colete de tecido feminino*1</t>
+  </si>
+  <si>
+    <t>Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1</t>
+  </si>
+  <si>
+    <t>Colar semi joia arvore da vida corrente veneziana verniz italiano*1</t>
+  </si>
+  <si>
+    <t>Colete de tecido feminino*1</t>
+  </si>
+  <si>
+    <t>Conjunto de pijama menino*1+Vestuário Masculino Infantil*1+Vestuário Masculino Infantil*1</t>
+  </si>
+  <si>
+    <t>Laxasfit T900 Smartwatch 2026 Nova Relógio Inteligente para pronta entrega- Frete Grátis*1</t>
+  </si>
+  <si>
+    <t>Camiseta Unissex Feminina Masculina Estampa Jesus é o Caminho Cristã Algodão Conforto Casual Estilo Dia a Dia Promoção*2</t>
   </si>
   <si>
     <t>Body Splash Desodorante Colônia 200ml Inspiração Alta Fixação - Sly Cosméticos*1</t>
   </si>
   <si>
+    <t>Conjunto Cropped Tomara que Caia + Calça Wide Leg Listras Laterais*1</t>
+  </si>
+  <si>
+    <t>Toalha*1+Toalha*1</t>
+  </si>
+  <si>
+    <t>Terno feminino de poliéster*1+Chinelos*1+calças de tecido feminino*1+Calçado desportivo*1</t>
+  </si>
+  <si>
+    <t>Calça Jeans MOM Feminina Cintura Alta Qualidade Premiun*1</t>
+  </si>
+  <si>
+    <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
+  </si>
+  <si>
+    <t>Camiseta feminina de tricô*1+Saia de tecido feminino*1</t>
+  </si>
+  <si>
+    <t>Bolsa Feminina Transversal Bolsa de Mão Casamento Clutch Alça Removivel Lançamento*1</t>
+  </si>
+  <si>
     <t>Kit 3 Calças Infantil Chimpa Flanelado Inverno 2 ao 16*1</t>
   </si>
   <si>
-    <t>Bolsa Feminina Transversal Bolsa de Mão Casamento Clutch Alça Removivel Lançamento*1</t>
-  </si>
-  <si>
-    <t>Carregador Portátil Pineng Power Bank 10.000mah,5000mah com adaptador iPhone,V8*1</t>
-  </si>
-  <si>
-    <t>Novo modelo 2026 Fone de ouvido Bluetooth inteligente TWS M90pro e M88, versão 5.3, com display digital de bateria integrada e 3 cabos de dados — ideal para carregar seu celular Android, iPhone ou dispositivo Type-C em qualquer lugar, funci*2</t>
-  </si>
-  <si>
-    <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
-  </si>
-  <si>
-    <t>Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1+Edredom Sherpa Cobertor Manta Coberdrom Casal Queen Dupla Face Pele de Carneiro Grosso*1</t>
-  </si>
-  <si>
-    <t>Maquina Cortar Cabelo KM Profissional Grafites Max-2092 Cor Estampada*1</t>
-  </si>
-  <si>
-    <t>Body Feminino Renda Manga Longa Tendência*1</t>
-  </si>
-  <si>
-    <t>Meia 3D Divertida Infantil Cano Alto Com Desenho Animado–Meias até o joelho com estampa 3D | Alta qualidade, presente perfeito para meninas/mininos,Tamanho Único Veste 32 ao 38*1</t>
-  </si>
-  <si>
-    <t>Colar semi joia arvore da vida corrente veneziana verniz italiano*1</t>
-  </si>
-  <si>
-    <t>Conjunto de pijama menino*1+Vestuário Masculino Infantil*1+Vestuário Masculino Infantil*1</t>
-  </si>
-  <si>
-    <t>Sweatshirt de malha masculina*1+calças de tecido feminino*1+Blusa Feminina de Tecido*1+Calças Masculinas*1</t>
-  </si>
-  <si>
-    <t>Calça Jeans MOM Feminina Cintura Alta Qualidade Premiun*1</t>
-  </si>
-  <si>
-    <t>Body Renda Floral Manga Longa Tule Transparente Moda Feminina Inverno Sexy*1</t>
-  </si>
-  <si>
-    <t>Cicatribem Clareador Dérmico 60g – Hidratante Uniformizador e Revitalizante Facial e Corporal*1</t>
+    <t>Mini Potes para Congelar Papinha c/ Tampa Hermética Porta Leita em pó Frutas para Bebe adultos*1</t>
+  </si>
+  <si>
+    <t>Terno masculino*1</t>
+  </si>
+  <si>
+    <t>Macaquinho Flashline Preto*1+Macaquinho New Fluity Botanical*1</t>
+  </si>
+  <si>
+    <t>Pen Drive Para Celular Tipo C Dual Drive Para Backup Android e Iphone*1</t>
   </si>
   <si>
     <t>Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1</t>
   </si>
   <si>
-    <t>Terno masculino*1</t>
-  </si>
-  <si>
-    <t>KIT 3 Calça Jeans Feminina Wide Leg pantalona Cintura Alta Oferta especial entrega em 24 horas Outlet de fábrica*1</t>
-  </si>
-  <si>
     <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
-  </si>
-  <si>
-    <t>Porta Organizador De Mesa Coelhos Fofo Gaveta Treco Maquiagem De Mesa Pequeno Multifuncional Estilo Minimalista*1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,19 +489,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -488,7 +535,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -520,27 +567,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -572,24 +601,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -765,14 +776,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -792,227 +800,224 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1020,19 +1025,19 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1040,180 +1045,279 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ac909cf066e6b0f/Desktop/bots/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_23F921EDF3730C14266008E9C5CA0D686D7C8141" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B48C7625-ECB0-4E07-833E-49444BD76A38}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="138">
   <si>
     <t>AWB</t>
   </si>
@@ -109,9 +120,6 @@
     <t>6041626861261</t>
   </si>
   <si>
-    <t>3320090359776</t>
-  </si>
-  <si>
     <t>(JML INT)WINDISON MAICON - ITABIRA</t>
   </si>
   <si>
@@ -145,9 +153,6 @@
     <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
   </si>
   <si>
-    <t>(JML LOC) LUCAS FELIPE GOMES DA SILVA</t>
-  </si>
-  <si>
     <t>Adrielle Gonçalves</t>
   </si>
   <si>
@@ -220,9 +225,6 @@
     <t>Marina Soares Assunção</t>
   </si>
   <si>
-    <t>eneluciafreitas</t>
-  </si>
-  <si>
     <t>+5557197062753</t>
   </si>
   <si>
@@ -292,9 +294,6 @@
     <t>+5531996590550</t>
   </si>
   <si>
-    <t>+5531998675818</t>
-  </si>
-  <si>
     <t>Rua Três 207 casa, Barreiro, Itabira</t>
   </si>
   <si>
@@ -367,9 +366,6 @@
     <t>Rua Fernando Dias de Carvalho 305, Centro, Ferros</t>
   </si>
   <si>
-    <t>Rua Colatina 393, Industrial, João Monlevade</t>
-  </si>
-  <si>
     <t>Carregador Portátil Pineng Power Bank 10.000mah,5000mah com adaptador iPhone,V8*1</t>
   </si>
   <si>
@@ -443,17 +439,22 @@
   </si>
   <si>
     <t>Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1</t>
-  </si>
-  <si>
-    <t>Sutiã Tomara que Caia Invisível Efeito Silicone Lib Push Up Anti-Suor para Vestidos e Festas*1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -481,19 +482,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -535,7 +545,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -567,9 +577,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -601,6 +629,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -776,11 +822,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -800,523 +846,504 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" t="s">
-        <v>117</v>
-      </c>
-      <c r="F27" t="s">
-        <v>143</v>
-      </c>
-    </row>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dados_acareacoes.xlsx
+++ b/dados_acareacoes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="89">
   <si>
     <t>AWB</t>
   </si>
@@ -37,102 +37,126 @@
     <t>Valor</t>
   </si>
   <si>
+    <t>3320017369565</t>
+  </si>
+  <si>
+    <t>6041626861261</t>
+  </si>
+  <si>
+    <t>6041626242474</t>
+  </si>
+  <si>
+    <t>6041626588141</t>
+  </si>
+  <si>
+    <t>3320065356023</t>
+  </si>
+  <si>
+    <t>3320012332180</t>
+  </si>
+  <si>
+    <t>6041726804719</t>
+  </si>
+  <si>
+    <t>6041826674013</t>
+  </si>
+  <si>
+    <t>3320034361855</t>
+  </si>
+  <si>
+    <t>3320087368166</t>
+  </si>
+  <si>
+    <t>3320078356129</t>
+  </si>
+  <si>
+    <t>3320093344210</t>
+  </si>
+  <si>
+    <t>3320090369854</t>
+  </si>
+  <si>
     <t>3320098367249</t>
   </si>
   <si>
-    <t>6041726804719</t>
-  </si>
-  <si>
-    <t>6041626861261</t>
-  </si>
-  <si>
-    <t>6041626242474</t>
-  </si>
-  <si>
     <t>6040226346133</t>
   </si>
   <si>
-    <t>6041826674013</t>
-  </si>
-  <si>
-    <t>3320034361855</t>
-  </si>
-  <si>
-    <t>3320087368166</t>
-  </si>
-  <si>
-    <t>6041426892552</t>
-  </si>
-  <si>
-    <t>6041626588141</t>
-  </si>
-  <si>
-    <t>(JML LOC) LUCAS DE SOUZA SILVA</t>
+    <t>(JML INT)WINDISON MAICON - ITABIRA</t>
+  </si>
+  <si>
+    <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
+  </si>
+  <si>
+    <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
+  </si>
+  <si>
+    <t>(JML LOC) MATEUS ALEXANDRE DA SILVA</t>
   </si>
   <si>
     <t>(JML INT)GETER HENRIQUE - ITABIRA</t>
   </si>
   <si>
-    <t>(JML INT) SERGIO DE ALMEIDA - ROÇA</t>
-  </si>
-  <si>
-    <t>(JML INT)WINDISON MAICON - ITABIRA</t>
-  </si>
-  <si>
-    <t>(JML INT)WENDERSON ARAUJO - ITABIRA</t>
-  </si>
-  <si>
     <t>(JML LOC) MARC RODRIGO DA COSTA SILVA</t>
   </si>
   <si>
     <t>(STB LOC)MARCOS AURELIO BRAGA JUNIOR</t>
   </si>
   <si>
-    <t>(JML INT)WHEMES LEMOS - SÃO GONÇALO</t>
-  </si>
-  <si>
-    <t>Ramieller Douglas</t>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Marina Soares Assunção</t>
+  </si>
+  <si>
+    <t>Maira Almeida</t>
+  </si>
+  <si>
+    <t>Aline Oliveira Silva</t>
+  </si>
+  <si>
+    <t>Sophia Rodrigues</t>
+  </si>
+  <si>
+    <t>Sunamita Oliveira Oliveira</t>
   </si>
   <si>
     <t>Cláudia Simões</t>
   </si>
   <si>
-    <t>Marina Soares Assunção</t>
-  </si>
-  <si>
-    <t>Maira Almeida</t>
-  </si>
-  <si>
-    <t>Beatriz Azevedo Barcelos</t>
-  </si>
-  <si>
     <t>Juçara Martins de Paula</t>
   </si>
   <si>
     <t>liza mãe João Miguel</t>
   </si>
   <si>
-    <t>Soleane Ferreira Quites</t>
-  </si>
-  <si>
-    <t>Aline Oliveira Silva</t>
-  </si>
-  <si>
-    <t>+5531975092030</t>
+    <t>Cleonice Gomes</t>
+  </si>
+  <si>
+    <t>+5531980264961</t>
+  </si>
+  <si>
+    <t>+5531996590550</t>
+  </si>
+  <si>
+    <t>+5531997712507</t>
+  </si>
+  <si>
+    <t>+5531986384873</t>
+  </si>
+  <si>
+    <t>+5531972004262</t>
+  </si>
+  <si>
+    <t>+5531997405709</t>
   </si>
   <si>
     <t>+5531987408609</t>
   </si>
   <si>
-    <t>+5531996590550</t>
-  </si>
-  <si>
-    <t>+5531997712507</t>
-  </si>
-  <si>
-    <t>+5531991914681</t>
-  </si>
-  <si>
     <t>+5531997036776</t>
   </si>
   <si>
@@ -142,57 +166,72 @@
     <t>+5531996688180</t>
   </si>
   <si>
-    <t>+5531996661097</t>
-  </si>
-  <si>
-    <t>+5531986384873</t>
+    <t>Rua B 67 casa, João XXIII, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Fernando Dias de Carvalho 305, Centro, Ferros</t>
+  </si>
+  <si>
+    <t>Rua Raul Pompéia, João XXIII, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Valdemar de Alvarenga Lage- até 716/717 Loja LG Confecções, Água Fresca, Itabira</t>
+  </si>
+  <si>
+    <t>Rua Renato Campos 27 Casa, Campestre I, Itabira</t>
+  </si>
+  <si>
+    <t>Rua João Camilo de Oliveira Torres 840 Ap 403 bloco 08, Praia, Itabira</t>
+  </si>
+  <si>
+    <t>Avenida Pedro Martins Guerra 1325, Gabiroba (1ª Seção), Itabira</t>
+  </si>
+  <si>
+    <t>Rua Monte Castelo Próximo à igreja Batista, Belmonte, João Monlevade</t>
+  </si>
+  <si>
+    <t>Rua Nélson Figueiredo 86 casa fundos portão vermelho, Eldorado, Itabira</t>
+  </si>
+  <si>
+    <t>Terminal rodoviário São João do morro grande 1 Rodoviária, Avenida Wilson Alvarenga 190, Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Rua Cônego José Lopes Magalhães s/n casa, Eldorado, Itabira</t>
+  </si>
+  <si>
+    <t>Cônego guillherminio pereira 234 casa, bela vista, Itabira</t>
+  </si>
+  <si>
+    <t>rua São Sebastião 83, Docelino, Nova União</t>
   </si>
   <si>
     <t>Rua Industrial 400, Rosário, João Monlevade</t>
   </si>
   <si>
-    <t>Avenida Pedro Martins Guerra 1325, Gabiroba (1ª Seção), Itabira</t>
-  </si>
-  <si>
-    <t>Rua Fernando Dias de Carvalho 305, Centro, Ferros</t>
-  </si>
-  <si>
-    <t>Rua Raul Pompéia, João XXIII, Itabira</t>
-  </si>
-  <si>
     <t>Avenida France de Paula Andrade- número 35a, Vila Paciência Casa, Vila Nações Unidas, Itabira</t>
   </si>
   <si>
-    <t>Rua Monte Castelo Próximo à igreja Batista, Belmonte, João Monlevade</t>
-  </si>
-  <si>
-    <t>Rua Nélson Figueiredo 86 casa fundos portão vermelho, Eldorado, Itabira</t>
-  </si>
-  <si>
-    <t>Terminal rodoviário São João do morro grande 1 Rodoviária, Avenida Wilson Alvarenga 190, Barão de Cocais</t>
-  </si>
-  <si>
-    <t>Sitio faxina Casa, Faxina, São Gonçalo do Rio Abaixo</t>
-  </si>
-  <si>
-    <t>Rua Valdemar de Alvarenga Lage- até 716/717 Loja LG Confecções, Água Fresca, Itabira</t>
-  </si>
-  <si>
-    <t>Pen Drive Para Celular Tipo C Dual Drive Para Backup Android e Iphone*1</t>
+    <t>Balança De Cozinha Digital Alta Precisão Até 10kg Capacidade máxima 10 g Cor Branco*1</t>
+  </si>
+  <si>
+    <t>Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1</t>
+  </si>
+  <si>
+    <t>Camiseta feminina de tricô*1+Saia de tecido feminino*1</t>
+  </si>
+  <si>
+    <t>Colete de tecido feminino*1</t>
+  </si>
+  <si>
+    <t>Colar com fotos Colar Relicário Prata 925 coração banhado presente romantico*1</t>
+  </si>
+  <si>
+    <t>12 Hastes Guarda Chuva Automático Sombrinha Grande Proteção Solar UV Reforçado Dobrável Envio Imediato colorido*1</t>
   </si>
   <si>
     <t>Acessórios para bicicletas*1+Jaqueta feminina de tecido*1+calças de tecido feminino*1+Jaqueta feminina de tecido*1+Saco de armazenamento*1</t>
   </si>
   <si>
-    <t>Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1+Camiseta feminina de tricô*1</t>
-  </si>
-  <si>
-    <t>Camiseta feminina de tricô*1+Saia de tecido feminino*1</t>
-  </si>
-  <si>
-    <t>Toalha*1+Toalha*1</t>
-  </si>
-  <si>
     <t>Conjunto de pijama menino*1+Vestuário Masculino Infantil*1+Vestuário Masculino Infantil*1</t>
   </si>
   <si>
@@ -202,40 +241,46 @@
     <t>Porta Organizador De Mesa Coelhos Fofo Gaveta Treco Maquiagem De Mesa Pequeno Multifuncional Estilo Minimalista*1</t>
   </si>
   <si>
-    <t>Terno masculino*1</t>
-  </si>
-  <si>
-    <t>Colete de tecido feminino*1</t>
-  </si>
-  <si>
-    <t>66.75</t>
+    <t>****</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>114.16</t>
+  </si>
+  <si>
+    <t>22.4</t>
+  </si>
+  <si>
+    <t>73.99</t>
+  </si>
+  <si>
+    <t>56.91</t>
+  </si>
+  <si>
+    <t>2.8</t>
   </si>
   <si>
     <t>198.07</t>
   </si>
   <si>
-    <t>114.16</t>
-  </si>
-  <si>
-    <t>22.4</t>
+    <t>280.18</t>
+  </si>
+  <si>
+    <t>38.43</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>75.69</t>
+  </si>
+  <si>
+    <t>1.3</t>
   </si>
   <si>
     <t>19.96</t>
-  </si>
-  <si>
-    <t>280.18</t>
-  </si>
-  <si>
-    <t>38.43</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>9.89</t>
-  </si>
-  <si>
-    <t>73.99</t>
   </si>
 </sst>
 </file>
@@ -567,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -598,22 +643,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -621,22 +666,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -644,22 +689,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -667,22 +712,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -690,22 +735,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -713,22 +758,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -736,22 +781,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -759,19 +804,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -782,19 +830,19 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -802,22 +850,107 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" t="s">
-        <v>73</v>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
